--- a/templates/SALES_BM_TEMPLATE.xlsx
+++ b/templates/SALES_BM_TEMPLATE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t>Date</t>
   </si>
@@ -98,22 +98,19 @@
     <t>Colour</t>
   </si>
   <si>
-    <t>BM-EXAMPLE</t>
+    <t>BM-7781</t>
   </si>
   <si>
-    <t>SG-A23-128-BK-EX</t>
+    <t>S22-128-GRN</t>
   </si>
   <si>
-    <t>350100000000001</t>
+    <t>350100000015838</t>
   </si>
   <si>
-    <t>EXAMPLE SUPPLIER</t>
+    <t>PHONEBOX DIRECT</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>Samsung Galaxy A23 128GB</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -580,7 +577,7 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
         <v>32</v>
@@ -588,66 +585,66 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>40</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>50</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -767,10 +764,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="3">
-        <v>73</v>
+        <v>240</v>
       </c>
       <c r="H2" s="3">
-        <v>129</v>
+        <v>329</v>
       </c>
       <c r="I2" s="3">
         <f>IF($H2="","",H2-G2)</f>
@@ -785,7 +782,7 @@
         <v>8.99</v>
       </c>
       <c r="M2" s="3">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="N2" s="3">
         <f>IF($H2="","",M2*20%)</f>
@@ -806,7 +803,7 @@
         <v>32</v>
       </c>
       <c r="T2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="Z2" s="3">
         <f>IF($H2="","",P2-Y2)</f>
@@ -8220,7 +8217,7 @@
     </row>
     <row r="203" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>

--- a/templates/SALES_BM_TEMPLATE.xlsx
+++ b/templates/SALES_BM_TEMPLATE.xlsx
@@ -770,13 +770,13 @@
         <v>329</v>
       </c>
       <c r="I2" s="3">
-        <f>IF($H2="","",H2-G2)</f>
+        <f>H2-G2</f>
       </c>
       <c r="J2" s="3">
-        <f>IF($H2="","",I2*16.67%)</f>
+        <f>I2*16.67%</f>
       </c>
       <c r="K2" s="3">
-        <f>IF($H2="","",H2/100*11)</f>
+        <f>H2/100*11</f>
       </c>
       <c r="L2" s="3">
         <v>8.99</v>
@@ -785,19 +785,19 @@
         <v>8</v>
       </c>
       <c r="N2" s="3">
-        <f>IF($H2="","",M2*20%)</f>
+        <f>M2*20%</f>
       </c>
       <c r="O2" s="3">
         <v>1</v>
       </c>
       <c r="P2" s="3">
-        <f>IF($H2="","",I2-J2-K2-L2-M2-N2-O2)</f>
+        <f>I2-J2-K2-L2-M2-N2-O2</f>
       </c>
       <c r="Q2" s="3">
-        <f>IF($H2="","",(P2-Y2)/G2*100)</f>
+        <f>(P2-Y2)/G2*100</f>
       </c>
       <c r="R2" s="3">
-        <f>IF($H2="","",J2-N2)</f>
+        <f>J2-N2</f>
       </c>
       <c r="S2" t="s">
         <v>32</v>
@@ -806,7 +806,7 @@
         <v>29</v>
       </c>
       <c r="Z2" s="3">
-        <f>IF($H2="","",P2-Y2)</f>
+        <f>P2-Y2</f>
       </c>
       <c r="AA2" t="s">
         <v>32</v>
@@ -815,7 +815,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="D3" s="2"/>
       <c r="G3" s="3"/>
@@ -852,7 +852,7 @@
         <f>IF($H3="","",P3-Y3)</f>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="D4" s="2"/>
       <c r="G4" s="3"/>
@@ -889,7 +889,7 @@
         <f>IF($H4="","",P4-Y4)</f>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="D5" s="2"/>
       <c r="G5" s="3"/>
@@ -926,7 +926,7 @@
         <f>IF($H5="","",P5-Y5)</f>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="D6" s="2"/>
       <c r="G6" s="3"/>
@@ -963,7 +963,7 @@
         <f>IF($H6="","",P6-Y6)</f>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="D7" s="2"/>
       <c r="G7" s="3"/>
@@ -1000,7 +1000,7 @@
         <f>IF($H7="","",P7-Y7)</f>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="D8" s="2"/>
       <c r="G8" s="3"/>
@@ -1037,7 +1037,7 @@
         <f>IF($H8="","",P8-Y8)</f>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="D9" s="2"/>
       <c r="G9" s="3"/>
@@ -1074,7 +1074,7 @@
         <f>IF($H9="","",P9-Y9)</f>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="D10" s="2"/>
       <c r="G10" s="3"/>
@@ -1111,7 +1111,7 @@
         <f>IF($H10="","",P10-Y10)</f>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="D11" s="2"/>
       <c r="G11" s="3"/>
@@ -1148,7 +1148,7 @@
         <f>IF($H11="","",P11-Y11)</f>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="D12" s="2"/>
       <c r="G12" s="3"/>
@@ -1185,7 +1185,7 @@
         <f>IF($H12="","",P12-Y12)</f>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="D13" s="2"/>
       <c r="G13" s="3"/>
@@ -1222,7 +1222,7 @@
         <f>IF($H13="","",P13-Y13)</f>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="2"/>
       <c r="G14" s="3"/>
@@ -1259,7 +1259,7 @@
         <f>IF($H14="","",P14-Y14)</f>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="D15" s="2"/>
       <c r="G15" s="3"/>
@@ -1296,7 +1296,7 @@
         <f>IF($H15="","",P15-Y15)</f>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="D16" s="2"/>
       <c r="G16" s="3"/>
@@ -1333,7 +1333,7 @@
         <f>IF($H16="","",P16-Y16)</f>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="D17" s="2"/>
       <c r="G17" s="3"/>
@@ -1370,7 +1370,7 @@
         <f>IF($H17="","",P17-Y17)</f>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="D18" s="2"/>
       <c r="G18" s="3"/>
@@ -1407,7 +1407,7 @@
         <f>IF($H18="","",P18-Y18)</f>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="D19" s="2"/>
       <c r="G19" s="3"/>
@@ -1444,7 +1444,7 @@
         <f>IF($H19="","",P19-Y19)</f>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="D20" s="2"/>
       <c r="G20" s="3"/>
@@ -1481,7 +1481,7 @@
         <f>IF($H20="","",P20-Y20)</f>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="D21" s="2"/>
       <c r="G21" s="3"/>
@@ -1518,7 +1518,7 @@
         <f>IF($H21="","",P21-Y21)</f>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="D22" s="2"/>
       <c r="G22" s="3"/>
@@ -1555,7 +1555,7 @@
         <f>IF($H22="","",P22-Y22)</f>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="D23" s="2"/>
       <c r="G23" s="3"/>
@@ -1592,7 +1592,7 @@
         <f>IF($H23="","",P23-Y23)</f>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="D24" s="2"/>
       <c r="G24" s="3"/>
@@ -1629,7 +1629,7 @@
         <f>IF($H24="","",P24-Y24)</f>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="D25" s="2"/>
       <c r="G25" s="3"/>
@@ -1666,7 +1666,7 @@
         <f>IF($H25="","",P25-Y25)</f>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="D26" s="2"/>
       <c r="G26" s="3"/>
@@ -1703,7 +1703,7 @@
         <f>IF($H26="","",P26-Y26)</f>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="D27" s="2"/>
       <c r="G27" s="3"/>
@@ -1740,7 +1740,7 @@
         <f>IF($H27="","",P27-Y27)</f>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="D28" s="2"/>
       <c r="G28" s="3"/>
@@ -1777,7 +1777,7 @@
         <f>IF($H28="","",P28-Y28)</f>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="D29" s="2"/>
       <c r="G29" s="3"/>
@@ -1814,7 +1814,7 @@
         <f>IF($H29="","",P29-Y29)</f>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="D30" s="2"/>
       <c r="G30" s="3"/>
@@ -1851,7 +1851,7 @@
         <f>IF($H30="","",P30-Y30)</f>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="D31" s="2"/>
       <c r="G31" s="3"/>
@@ -1888,7 +1888,7 @@
         <f>IF($H31="","",P31-Y31)</f>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="D32" s="2"/>
       <c r="G32" s="3"/>
@@ -1925,7 +1925,7 @@
         <f>IF($H32="","",P32-Y32)</f>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="D33" s="2"/>
       <c r="G33" s="3"/>
@@ -1962,7 +1962,7 @@
         <f>IF($H33="","",P33-Y33)</f>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="D34" s="2"/>
       <c r="G34" s="3"/>
@@ -1999,7 +1999,7 @@
         <f>IF($H34="","",P34-Y34)</f>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="D35" s="2"/>
       <c r="G35" s="3"/>
@@ -2036,7 +2036,7 @@
         <f>IF($H35="","",P35-Y35)</f>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="D36" s="2"/>
       <c r="G36" s="3"/>
@@ -2073,7 +2073,7 @@
         <f>IF($H36="","",P36-Y36)</f>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="D37" s="2"/>
       <c r="G37" s="3"/>
@@ -2110,7 +2110,7 @@
         <f>IF($H37="","",P37-Y37)</f>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="D38" s="2"/>
       <c r="G38" s="3"/>
@@ -2147,7 +2147,7 @@
         <f>IF($H38="","",P38-Y38)</f>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="D39" s="2"/>
       <c r="G39" s="3"/>
@@ -2184,7 +2184,7 @@
         <f>IF($H39="","",P39-Y39)</f>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="D40" s="2"/>
       <c r="G40" s="3"/>
@@ -2221,7 +2221,7 @@
         <f>IF($H40="","",P40-Y40)</f>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="D41" s="2"/>
       <c r="G41" s="3"/>
@@ -2258,7 +2258,7 @@
         <f>IF($H41="","",P41-Y41)</f>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="D42" s="2"/>
       <c r="G42" s="3"/>
@@ -2295,7 +2295,7 @@
         <f>IF($H42="","",P42-Y42)</f>
       </c>
     </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="D43" s="2"/>
       <c r="G43" s="3"/>
@@ -2332,7 +2332,7 @@
         <f>IF($H43="","",P43-Y43)</f>
       </c>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="D44" s="2"/>
       <c r="G44" s="3"/>
@@ -2369,7 +2369,7 @@
         <f>IF($H44="","",P44-Y44)</f>
       </c>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="D45" s="2"/>
       <c r="G45" s="3"/>
@@ -2406,7 +2406,7 @@
         <f>IF($H45="","",P45-Y45)</f>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="D46" s="2"/>
       <c r="G46" s="3"/>
@@ -2443,7 +2443,7 @@
         <f>IF($H46="","",P46-Y46)</f>
       </c>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="D47" s="2"/>
       <c r="G47" s="3"/>
@@ -2480,7 +2480,7 @@
         <f>IF($H47="","",P47-Y47)</f>
       </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="D48" s="2"/>
       <c r="G48" s="3"/>
@@ -2517,7 +2517,7 @@
         <f>IF($H48="","",P48-Y48)</f>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="D49" s="2"/>
       <c r="G49" s="3"/>
@@ -2554,7 +2554,7 @@
         <f>IF($H49="","",P49-Y49)</f>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="D50" s="2"/>
       <c r="G50" s="3"/>
@@ -2591,7 +2591,7 @@
         <f>IF($H50="","",P50-Y50)</f>
       </c>
     </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="D51" s="2"/>
       <c r="G51" s="3"/>
@@ -2628,7 +2628,7 @@
         <f>IF($H51="","",P51-Y51)</f>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="D52" s="2"/>
       <c r="G52" s="3"/>
@@ -2665,7 +2665,7 @@
         <f>IF($H52="","",P52-Y52)</f>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="D53" s="2"/>
       <c r="G53" s="3"/>
@@ -2702,7 +2702,7 @@
         <f>IF($H53="","",P53-Y53)</f>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="D54" s="2"/>
       <c r="G54" s="3"/>
@@ -2739,7 +2739,7 @@
         <f>IF($H54="","",P54-Y54)</f>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="D55" s="2"/>
       <c r="G55" s="3"/>
@@ -2776,7 +2776,7 @@
         <f>IF($H55="","",P55-Y55)</f>
       </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="D56" s="2"/>
       <c r="G56" s="3"/>
@@ -2813,7 +2813,7 @@
         <f>IF($H56="","",P56-Y56)</f>
       </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="D57" s="2"/>
       <c r="G57" s="3"/>
@@ -2850,7 +2850,7 @@
         <f>IF($H57="","",P57-Y57)</f>
       </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="D58" s="2"/>
       <c r="G58" s="3"/>
@@ -2887,7 +2887,7 @@
         <f>IF($H58="","",P58-Y58)</f>
       </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="D59" s="2"/>
       <c r="G59" s="3"/>
@@ -2924,7 +2924,7 @@
         <f>IF($H59="","",P59-Y59)</f>
       </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="D60" s="2"/>
       <c r="G60" s="3"/>
@@ -2961,7 +2961,7 @@
         <f>IF($H60="","",P60-Y60)</f>
       </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="D61" s="2"/>
       <c r="G61" s="3"/>
@@ -2998,7 +2998,7 @@
         <f>IF($H61="","",P61-Y61)</f>
       </c>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="D62" s="2"/>
       <c r="G62" s="3"/>
@@ -3035,7 +3035,7 @@
         <f>IF($H62="","",P62-Y62)</f>
       </c>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="D63" s="2"/>
       <c r="G63" s="3"/>
@@ -3072,7 +3072,7 @@
         <f>IF($H63="","",P63-Y63)</f>
       </c>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="D64" s="2"/>
       <c r="G64" s="3"/>
@@ -3109,7 +3109,7 @@
         <f>IF($H64="","",P64-Y64)</f>
       </c>
     </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="D65" s="2"/>
       <c r="G65" s="3"/>
@@ -3146,7 +3146,7 @@
         <f>IF($H65="","",P65-Y65)</f>
       </c>
     </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="D66" s="2"/>
       <c r="G66" s="3"/>
@@ -3183,7 +3183,7 @@
         <f>IF($H66="","",P66-Y66)</f>
       </c>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="D67" s="2"/>
       <c r="G67" s="3"/>
@@ -3220,7 +3220,7 @@
         <f>IF($H67="","",P67-Y67)</f>
       </c>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="D68" s="2"/>
       <c r="G68" s="3"/>
@@ -3257,7 +3257,7 @@
         <f>IF($H68="","",P68-Y68)</f>
       </c>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="D69" s="2"/>
       <c r="G69" s="3"/>
@@ -3294,7 +3294,7 @@
         <f>IF($H69="","",P69-Y69)</f>
       </c>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="D70" s="2"/>
       <c r="G70" s="3"/>
@@ -3331,7 +3331,7 @@
         <f>IF($H70="","",P70-Y70)</f>
       </c>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="D71" s="2"/>
       <c r="G71" s="3"/>
@@ -3368,7 +3368,7 @@
         <f>IF($H71="","",P71-Y71)</f>
       </c>
     </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="D72" s="2"/>
       <c r="G72" s="3"/>
@@ -3405,7 +3405,7 @@
         <f>IF($H72="","",P72-Y72)</f>
       </c>
     </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="D73" s="2"/>
       <c r="G73" s="3"/>
@@ -3442,7 +3442,7 @@
         <f>IF($H73="","",P73-Y73)</f>
       </c>
     </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="D74" s="2"/>
       <c r="G74" s="3"/>
@@ -3479,7 +3479,7 @@
         <f>IF($H74="","",P74-Y74)</f>
       </c>
     </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="D75" s="2"/>
       <c r="G75" s="3"/>
@@ -3516,7 +3516,7 @@
         <f>IF($H75="","",P75-Y75)</f>
       </c>
     </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="D76" s="2"/>
       <c r="G76" s="3"/>
@@ -3553,7 +3553,7 @@
         <f>IF($H76="","",P76-Y76)</f>
       </c>
     </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="D77" s="2"/>
       <c r="G77" s="3"/>
@@ -3590,7 +3590,7 @@
         <f>IF($H77="","",P77-Y77)</f>
       </c>
     </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="D78" s="2"/>
       <c r="G78" s="3"/>
@@ -3627,7 +3627,7 @@
         <f>IF($H78="","",P78-Y78)</f>
       </c>
     </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="D79" s="2"/>
       <c r="G79" s="3"/>
@@ -3664,7 +3664,7 @@
         <f>IF($H79="","",P79-Y79)</f>
       </c>
     </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="D80" s="2"/>
       <c r="G80" s="3"/>
@@ -3701,7 +3701,7 @@
         <f>IF($H80="","",P80-Y80)</f>
       </c>
     </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="D81" s="2"/>
       <c r="G81" s="3"/>
@@ -3738,7 +3738,7 @@
         <f>IF($H81="","",P81-Y81)</f>
       </c>
     </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="D82" s="2"/>
       <c r="G82" s="3"/>
@@ -3775,7 +3775,7 @@
         <f>IF($H82="","",P82-Y82)</f>
       </c>
     </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="D83" s="2"/>
       <c r="G83" s="3"/>
@@ -3812,7 +3812,7 @@
         <f>IF($H83="","",P83-Y83)</f>
       </c>
     </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="D84" s="2"/>
       <c r="G84" s="3"/>
@@ -3849,7 +3849,7 @@
         <f>IF($H84="","",P84-Y84)</f>
       </c>
     </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="D85" s="2"/>
       <c r="G85" s="3"/>
@@ -3886,7 +3886,7 @@
         <f>IF($H85="","",P85-Y85)</f>
       </c>
     </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="D86" s="2"/>
       <c r="G86" s="3"/>
@@ -3923,7 +3923,7 @@
         <f>IF($H86="","",P86-Y86)</f>
       </c>
     </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="D87" s="2"/>
       <c r="G87" s="3"/>
@@ -3960,7 +3960,7 @@
         <f>IF($H87="","",P87-Y87)</f>
       </c>
     </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="D88" s="2"/>
       <c r="G88" s="3"/>
@@ -3997,7 +3997,7 @@
         <f>IF($H88="","",P88-Y88)</f>
       </c>
     </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="D89" s="2"/>
       <c r="G89" s="3"/>
@@ -4034,7 +4034,7 @@
         <f>IF($H89="","",P89-Y89)</f>
       </c>
     </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="D90" s="2"/>
       <c r="G90" s="3"/>
@@ -4071,7 +4071,7 @@
         <f>IF($H90="","",P90-Y90)</f>
       </c>
     </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="D91" s="2"/>
       <c r="G91" s="3"/>
@@ -4108,7 +4108,7 @@
         <f>IF($H91="","",P91-Y91)</f>
       </c>
     </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="D92" s="2"/>
       <c r="G92" s="3"/>
@@ -4145,7 +4145,7 @@
         <f>IF($H92="","",P92-Y92)</f>
       </c>
     </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="D93" s="2"/>
       <c r="G93" s="3"/>
@@ -4182,7 +4182,7 @@
         <f>IF($H93="","",P93-Y93)</f>
       </c>
     </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="D94" s="2"/>
       <c r="G94" s="3"/>
@@ -4219,7 +4219,7 @@
         <f>IF($H94="","",P94-Y94)</f>
       </c>
     </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="D95" s="2"/>
       <c r="G95" s="3"/>
@@ -4256,7 +4256,7 @@
         <f>IF($H95="","",P95-Y95)</f>
       </c>
     </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="D96" s="2"/>
       <c r="G96" s="3"/>
@@ -4293,7 +4293,7 @@
         <f>IF($H96="","",P96-Y96)</f>
       </c>
     </row>
-    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="2"/>
       <c r="G97" s="3"/>
@@ -4330,7 +4330,7 @@
         <f>IF($H97="","",P97-Y97)</f>
       </c>
     </row>
-    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="D98" s="2"/>
       <c r="G98" s="3"/>
@@ -4367,7 +4367,7 @@
         <f>IF($H98="","",P98-Y98)</f>
       </c>
     </row>
-    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="D99" s="2"/>
       <c r="G99" s="3"/>
@@ -4404,7 +4404,7 @@
         <f>IF($H99="","",P99-Y99)</f>
       </c>
     </row>
-    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="D100" s="2"/>
       <c r="G100" s="3"/>
@@ -4441,7 +4441,7 @@
         <f>IF($H100="","",P100-Y100)</f>
       </c>
     </row>
-    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="D101" s="2"/>
       <c r="G101" s="3"/>
@@ -4478,7 +4478,7 @@
         <f>IF($H101="","",P101-Y101)</f>
       </c>
     </row>
-    <row r="102" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="D102" s="2"/>
       <c r="G102" s="3"/>
@@ -4515,7 +4515,7 @@
         <f>IF($H102="","",P102-Y102)</f>
       </c>
     </row>
-    <row r="103" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="D103" s="2"/>
       <c r="G103" s="3"/>
@@ -4552,7 +4552,7 @@
         <f>IF($H103="","",P103-Y103)</f>
       </c>
     </row>
-    <row r="104" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="D104" s="2"/>
       <c r="G104" s="3"/>
@@ -4589,7 +4589,7 @@
         <f>IF($H104="","",P104-Y104)</f>
       </c>
     </row>
-    <row r="105" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="D105" s="2"/>
       <c r="G105" s="3"/>
@@ -4626,7 +4626,7 @@
         <f>IF($H105="","",P105-Y105)</f>
       </c>
     </row>
-    <row r="106" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="D106" s="2"/>
       <c r="G106" s="3"/>
@@ -4663,7 +4663,7 @@
         <f>IF($H106="","",P106-Y106)</f>
       </c>
     </row>
-    <row r="107" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="D107" s="2"/>
       <c r="G107" s="3"/>
@@ -4700,7 +4700,7 @@
         <f>IF($H107="","",P107-Y107)</f>
       </c>
     </row>
-    <row r="108" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="D108" s="2"/>
       <c r="G108" s="3"/>
@@ -4737,7 +4737,7 @@
         <f>IF($H108="","",P108-Y108)</f>
       </c>
     </row>
-    <row r="109" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="D109" s="2"/>
       <c r="G109" s="3"/>
@@ -4774,7 +4774,7 @@
         <f>IF($H109="","",P109-Y109)</f>
       </c>
     </row>
-    <row r="110" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="D110" s="2"/>
       <c r="G110" s="3"/>
@@ -4811,7 +4811,7 @@
         <f>IF($H110="","",P110-Y110)</f>
       </c>
     </row>
-    <row r="111" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="D111" s="2"/>
       <c r="G111" s="3"/>
@@ -4848,7 +4848,7 @@
         <f>IF($H111="","",P111-Y111)</f>
       </c>
     </row>
-    <row r="112" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="D112" s="2"/>
       <c r="G112" s="3"/>
@@ -4885,7 +4885,7 @@
         <f>IF($H112="","",P112-Y112)</f>
       </c>
     </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="D113" s="2"/>
       <c r="G113" s="3"/>
@@ -4922,7 +4922,7 @@
         <f>IF($H113="","",P113-Y113)</f>
       </c>
     </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="D114" s="2"/>
       <c r="G114" s="3"/>
@@ -4959,7 +4959,7 @@
         <f>IF($H114="","",P114-Y114)</f>
       </c>
     </row>
-    <row r="115" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="D115" s="2"/>
       <c r="G115" s="3"/>
@@ -4996,7 +4996,7 @@
         <f>IF($H115="","",P115-Y115)</f>
       </c>
     </row>
-    <row r="116" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="D116" s="2"/>
       <c r="G116" s="3"/>
@@ -5033,7 +5033,7 @@
         <f>IF($H116="","",P116-Y116)</f>
       </c>
     </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="D117" s="2"/>
       <c r="G117" s="3"/>
@@ -5070,7 +5070,7 @@
         <f>IF($H117="","",P117-Y117)</f>
       </c>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="D118" s="2"/>
       <c r="G118" s="3"/>
@@ -5107,7 +5107,7 @@
         <f>IF($H118="","",P118-Y118)</f>
       </c>
     </row>
-    <row r="119" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="D119" s="2"/>
       <c r="G119" s="3"/>
@@ -5144,7 +5144,7 @@
         <f>IF($H119="","",P119-Y119)</f>
       </c>
     </row>
-    <row r="120" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="D120" s="2"/>
       <c r="G120" s="3"/>
@@ -5181,7 +5181,7 @@
         <f>IF($H120="","",P120-Y120)</f>
       </c>
     </row>
-    <row r="121" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="D121" s="2"/>
       <c r="G121" s="3"/>
@@ -5218,7 +5218,7 @@
         <f>IF($H121="","",P121-Y121)</f>
       </c>
     </row>
-    <row r="122" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="D122" s="2"/>
       <c r="G122" s="3"/>
@@ -5255,7 +5255,7 @@
         <f>IF($H122="","",P122-Y122)</f>
       </c>
     </row>
-    <row r="123" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="D123" s="2"/>
       <c r="G123" s="3"/>
@@ -5292,7 +5292,7 @@
         <f>IF($H123="","",P123-Y123)</f>
       </c>
     </row>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="D124" s="2"/>
       <c r="G124" s="3"/>
@@ -5329,7 +5329,7 @@
         <f>IF($H124="","",P124-Y124)</f>
       </c>
     </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="D125" s="2"/>
       <c r="G125" s="3"/>
@@ -5366,7 +5366,7 @@
         <f>IF($H125="","",P125-Y125)</f>
       </c>
     </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="D126" s="2"/>
       <c r="G126" s="3"/>
@@ -5403,7 +5403,7 @@
         <f>IF($H126="","",P126-Y126)</f>
       </c>
     </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="D127" s="2"/>
       <c r="G127" s="3"/>
@@ -5440,7 +5440,7 @@
         <f>IF($H127="","",P127-Y127)</f>
       </c>
     </row>
-    <row r="128" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="D128" s="2"/>
       <c r="G128" s="3"/>
@@ -5477,7 +5477,7 @@
         <f>IF($H128="","",P128-Y128)</f>
       </c>
     </row>
-    <row r="129" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="D129" s="2"/>
       <c r="G129" s="3"/>
@@ -5514,7 +5514,7 @@
         <f>IF($H129="","",P129-Y129)</f>
       </c>
     </row>
-    <row r="130" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="D130" s="2"/>
       <c r="G130" s="3"/>
@@ -5551,7 +5551,7 @@
         <f>IF($H130="","",P130-Y130)</f>
       </c>
     </row>
-    <row r="131" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="D131" s="2"/>
       <c r="G131" s="3"/>
@@ -5588,7 +5588,7 @@
         <f>IF($H131="","",P131-Y131)</f>
       </c>
     </row>
-    <row r="132" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="D132" s="2"/>
       <c r="G132" s="3"/>
@@ -5625,7 +5625,7 @@
         <f>IF($H132="","",P132-Y132)</f>
       </c>
     </row>
-    <row r="133" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="D133" s="2"/>
       <c r="G133" s="3"/>
@@ -5662,7 +5662,7 @@
         <f>IF($H133="","",P133-Y133)</f>
       </c>
     </row>
-    <row r="134" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="D134" s="2"/>
       <c r="G134" s="3"/>
@@ -5699,7 +5699,7 @@
         <f>IF($H134="","",P134-Y134)</f>
       </c>
     </row>
-    <row r="135" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="D135" s="2"/>
       <c r="G135" s="3"/>
@@ -5736,7 +5736,7 @@
         <f>IF($H135="","",P135-Y135)</f>
       </c>
     </row>
-    <row r="136" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="D136" s="2"/>
       <c r="G136" s="3"/>
@@ -5773,7 +5773,7 @@
         <f>IF($H136="","",P136-Y136)</f>
       </c>
     </row>
-    <row r="137" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="D137" s="2"/>
       <c r="G137" s="3"/>
@@ -5810,7 +5810,7 @@
         <f>IF($H137="","",P137-Y137)</f>
       </c>
     </row>
-    <row r="138" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="D138" s="2"/>
       <c r="G138" s="3"/>
@@ -5847,7 +5847,7 @@
         <f>IF($H138="","",P138-Y138)</f>
       </c>
     </row>
-    <row r="139" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="D139" s="2"/>
       <c r="G139" s="3"/>
@@ -5884,7 +5884,7 @@
         <f>IF($H139="","",P139-Y139)</f>
       </c>
     </row>
-    <row r="140" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="D140" s="2"/>
       <c r="G140" s="3"/>
@@ -5921,7 +5921,7 @@
         <f>IF($H140="","",P140-Y140)</f>
       </c>
     </row>
-    <row r="141" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="D141" s="2"/>
       <c r="G141" s="3"/>
@@ -5958,7 +5958,7 @@
         <f>IF($H141="","",P141-Y141)</f>
       </c>
     </row>
-    <row r="142" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="D142" s="2"/>
       <c r="G142" s="3"/>
@@ -5995,7 +5995,7 @@
         <f>IF($H142="","",P142-Y142)</f>
       </c>
     </row>
-    <row r="143" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="D143" s="2"/>
       <c r="G143" s="3"/>
@@ -6032,7 +6032,7 @@
         <f>IF($H143="","",P143-Y143)</f>
       </c>
     </row>
-    <row r="144" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="D144" s="2"/>
       <c r="G144" s="3"/>
@@ -6069,7 +6069,7 @@
         <f>IF($H144="","",P144-Y144)</f>
       </c>
     </row>
-    <row r="145" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="D145" s="2"/>
       <c r="G145" s="3"/>
@@ -6106,7 +6106,7 @@
         <f>IF($H145="","",P145-Y145)</f>
       </c>
     </row>
-    <row r="146" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="D146" s="2"/>
       <c r="G146" s="3"/>
@@ -6143,7 +6143,7 @@
         <f>IF($H146="","",P146-Y146)</f>
       </c>
     </row>
-    <row r="147" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="D147" s="2"/>
       <c r="G147" s="3"/>
@@ -6180,7 +6180,7 @@
         <f>IF($H147="","",P147-Y147)</f>
       </c>
     </row>
-    <row r="148" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="D148" s="2"/>
       <c r="G148" s="3"/>
@@ -6217,7 +6217,7 @@
         <f>IF($H148="","",P148-Y148)</f>
       </c>
     </row>
-    <row r="149" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="D149" s="2"/>
       <c r="G149" s="3"/>
@@ -6254,7 +6254,7 @@
         <f>IF($H149="","",P149-Y149)</f>
       </c>
     </row>
-    <row r="150" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="D150" s="2"/>
       <c r="G150" s="3"/>
@@ -6291,7 +6291,7 @@
         <f>IF($H150="","",P150-Y150)</f>
       </c>
     </row>
-    <row r="151" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="D151" s="2"/>
       <c r="G151" s="3"/>
@@ -6328,7 +6328,7 @@
         <f>IF($H151="","",P151-Y151)</f>
       </c>
     </row>
-    <row r="152" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="D152" s="2"/>
       <c r="G152" s="3"/>
@@ -6365,7 +6365,7 @@
         <f>IF($H152="","",P152-Y152)</f>
       </c>
     </row>
-    <row r="153" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="D153" s="2"/>
       <c r="G153" s="3"/>
@@ -6402,7 +6402,7 @@
         <f>IF($H153="","",P153-Y153)</f>
       </c>
     </row>
-    <row r="154" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="D154" s="2"/>
       <c r="G154" s="3"/>
@@ -6439,7 +6439,7 @@
         <f>IF($H154="","",P154-Y154)</f>
       </c>
     </row>
-    <row r="155" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="D155" s="2"/>
       <c r="G155" s="3"/>
@@ -6476,7 +6476,7 @@
         <f>IF($H155="","",P155-Y155)</f>
       </c>
     </row>
-    <row r="156" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="D156" s="2"/>
       <c r="G156" s="3"/>
@@ -6513,7 +6513,7 @@
         <f>IF($H156="","",P156-Y156)</f>
       </c>
     </row>
-    <row r="157" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="D157" s="2"/>
       <c r="G157" s="3"/>
@@ -6550,7 +6550,7 @@
         <f>IF($H157="","",P157-Y157)</f>
       </c>
     </row>
-    <row r="158" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="D158" s="2"/>
       <c r="G158" s="3"/>
@@ -6587,7 +6587,7 @@
         <f>IF($H158="","",P158-Y158)</f>
       </c>
     </row>
-    <row r="159" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="D159" s="2"/>
       <c r="G159" s="3"/>
@@ -6624,7 +6624,7 @@
         <f>IF($H159="","",P159-Y159)</f>
       </c>
     </row>
-    <row r="160" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="D160" s="2"/>
       <c r="G160" s="3"/>
@@ -6661,7 +6661,7 @@
         <f>IF($H160="","",P160-Y160)</f>
       </c>
     </row>
-    <row r="161" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="D161" s="2"/>
       <c r="G161" s="3"/>
@@ -6698,7 +6698,7 @@
         <f>IF($H161="","",P161-Y161)</f>
       </c>
     </row>
-    <row r="162" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="D162" s="2"/>
       <c r="G162" s="3"/>
@@ -6735,7 +6735,7 @@
         <f>IF($H162="","",P162-Y162)</f>
       </c>
     </row>
-    <row r="163" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="D163" s="2"/>
       <c r="G163" s="3"/>
@@ -6772,7 +6772,7 @@
         <f>IF($H163="","",P163-Y163)</f>
       </c>
     </row>
-    <row r="164" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="D164" s="2"/>
       <c r="G164" s="3"/>
@@ -6809,7 +6809,7 @@
         <f>IF($H164="","",P164-Y164)</f>
       </c>
     </row>
-    <row r="165" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="D165" s="2"/>
       <c r="G165" s="3"/>
@@ -6846,7 +6846,7 @@
         <f>IF($H165="","",P165-Y165)</f>
       </c>
     </row>
-    <row r="166" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="D166" s="2"/>
       <c r="G166" s="3"/>
@@ -6883,7 +6883,7 @@
         <f>IF($H166="","",P166-Y166)</f>
       </c>
     </row>
-    <row r="167" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="D167" s="2"/>
       <c r="G167" s="3"/>
@@ -6920,7 +6920,7 @@
         <f>IF($H167="","",P167-Y167)</f>
       </c>
     </row>
-    <row r="168" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="D168" s="2"/>
       <c r="G168" s="3"/>
@@ -6957,7 +6957,7 @@
         <f>IF($H168="","",P168-Y168)</f>
       </c>
     </row>
-    <row r="169" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="D169" s="2"/>
       <c r="G169" s="3"/>
@@ -6994,7 +6994,7 @@
         <f>IF($H169="","",P169-Y169)</f>
       </c>
     </row>
-    <row r="170" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="D170" s="2"/>
       <c r="G170" s="3"/>
@@ -7031,7 +7031,7 @@
         <f>IF($H170="","",P170-Y170)</f>
       </c>
     </row>
-    <row r="171" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="D171" s="2"/>
       <c r="G171" s="3"/>
@@ -7068,7 +7068,7 @@
         <f>IF($H171="","",P171-Y171)</f>
       </c>
     </row>
-    <row r="172" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="D172" s="2"/>
       <c r="G172" s="3"/>
@@ -7105,7 +7105,7 @@
         <f>IF($H172="","",P172-Y172)</f>
       </c>
     </row>
-    <row r="173" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="D173" s="2"/>
       <c r="G173" s="3"/>
@@ -7142,7 +7142,7 @@
         <f>IF($H173="","",P173-Y173)</f>
       </c>
     </row>
-    <row r="174" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="D174" s="2"/>
       <c r="G174" s="3"/>
@@ -7179,7 +7179,7 @@
         <f>IF($H174="","",P174-Y174)</f>
       </c>
     </row>
-    <row r="175" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="D175" s="2"/>
       <c r="G175" s="3"/>
@@ -7216,7 +7216,7 @@
         <f>IF($H175="","",P175-Y175)</f>
       </c>
     </row>
-    <row r="176" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="D176" s="2"/>
       <c r="G176" s="3"/>
@@ -7253,7 +7253,7 @@
         <f>IF($H176="","",P176-Y176)</f>
       </c>
     </row>
-    <row r="177" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="D177" s="2"/>
       <c r="G177" s="3"/>
@@ -7290,7 +7290,7 @@
         <f>IF($H177="","",P177-Y177)</f>
       </c>
     </row>
-    <row r="178" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="D178" s="2"/>
       <c r="G178" s="3"/>
@@ -7327,7 +7327,7 @@
         <f>IF($H178="","",P178-Y178)</f>
       </c>
     </row>
-    <row r="179" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="D179" s="2"/>
       <c r="G179" s="3"/>
@@ -7364,7 +7364,7 @@
         <f>IF($H179="","",P179-Y179)</f>
       </c>
     </row>
-    <row r="180" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="D180" s="2"/>
       <c r="G180" s="3"/>
@@ -7401,7 +7401,7 @@
         <f>IF($H180="","",P180-Y180)</f>
       </c>
     </row>
-    <row r="181" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="D181" s="2"/>
       <c r="G181" s="3"/>
@@ -7438,7 +7438,7 @@
         <f>IF($H181="","",P181-Y181)</f>
       </c>
     </row>
-    <row r="182" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="D182" s="2"/>
       <c r="G182" s="3"/>
@@ -7475,7 +7475,7 @@
         <f>IF($H182="","",P182-Y182)</f>
       </c>
     </row>
-    <row r="183" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="D183" s="2"/>
       <c r="G183" s="3"/>
@@ -7512,7 +7512,7 @@
         <f>IF($H183="","",P183-Y183)</f>
       </c>
     </row>
-    <row r="184" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="D184" s="2"/>
       <c r="G184" s="3"/>
@@ -7549,7 +7549,7 @@
         <f>IF($H184="","",P184-Y184)</f>
       </c>
     </row>
-    <row r="185" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="D185" s="2"/>
       <c r="G185" s="3"/>
@@ -7586,7 +7586,7 @@
         <f>IF($H185="","",P185-Y185)</f>
       </c>
     </row>
-    <row r="186" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="D186" s="2"/>
       <c r="G186" s="3"/>
@@ -7623,7 +7623,7 @@
         <f>IF($H186="","",P186-Y186)</f>
       </c>
     </row>
-    <row r="187" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="D187" s="2"/>
       <c r="G187" s="3"/>
@@ -7660,7 +7660,7 @@
         <f>IF($H187="","",P187-Y187)</f>
       </c>
     </row>
-    <row r="188" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="D188" s="2"/>
       <c r="G188" s="3"/>
@@ -7697,7 +7697,7 @@
         <f>IF($H188="","",P188-Y188)</f>
       </c>
     </row>
-    <row r="189" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="D189" s="2"/>
       <c r="G189" s="3"/>
@@ -7734,7 +7734,7 @@
         <f>IF($H189="","",P189-Y189)</f>
       </c>
     </row>
-    <row r="190" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="D190" s="2"/>
       <c r="G190" s="3"/>
@@ -7771,7 +7771,7 @@
         <f>IF($H190="","",P190-Y190)</f>
       </c>
     </row>
-    <row r="191" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="D191" s="2"/>
       <c r="G191" s="3"/>
@@ -7808,7 +7808,7 @@
         <f>IF($H191="","",P191-Y191)</f>
       </c>
     </row>
-    <row r="192" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="D192" s="2"/>
       <c r="G192" s="3"/>
@@ -7845,7 +7845,7 @@
         <f>IF($H192="","",P192-Y192)</f>
       </c>
     </row>
-    <row r="193" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="D193" s="2"/>
       <c r="G193" s="3"/>
@@ -7882,7 +7882,7 @@
         <f>IF($H193="","",P193-Y193)</f>
       </c>
     </row>
-    <row r="194" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="D194" s="2"/>
       <c r="G194" s="3"/>
@@ -7919,7 +7919,7 @@
         <f>IF($H194="","",P194-Y194)</f>
       </c>
     </row>
-    <row r="195" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="D195" s="2"/>
       <c r="G195" s="3"/>
@@ -7956,7 +7956,7 @@
         <f>IF($H195="","",P195-Y195)</f>
       </c>
     </row>
-    <row r="196" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="D196" s="2"/>
       <c r="G196" s="3"/>
@@ -7993,7 +7993,7 @@
         <f>IF($H196="","",P196-Y196)</f>
       </c>
     </row>
-    <row r="197" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="D197" s="2"/>
       <c r="G197" s="3"/>
@@ -8030,7 +8030,7 @@
         <f>IF($H197="","",P197-Y197)</f>
       </c>
     </row>
-    <row r="198" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="D198" s="2"/>
       <c r="G198" s="3"/>
@@ -8067,7 +8067,7 @@
         <f>IF($H198="","",P198-Y198)</f>
       </c>
     </row>
-    <row r="199" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="D199" s="2"/>
       <c r="G199" s="3"/>
@@ -8104,7 +8104,7 @@
         <f>IF($H199="","",P199-Y199)</f>
       </c>
     </row>
-    <row r="200" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="D200" s="2"/>
       <c r="G200" s="3"/>
@@ -8141,7 +8141,7 @@
         <f>IF($H200="","",P200-Y200)</f>
       </c>
     </row>
-    <row r="201" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="D201" s="2"/>
       <c r="G201" s="3"/>
@@ -8178,7 +8178,7 @@
         <f>IF($H201="","",P201-Y201)</f>
       </c>
     </row>
-    <row r="202" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="D202" s="2"/>
       <c r="G202" s="3"/>

--- a/templates/SALES_BM_TEMPLATE.xlsx
+++ b/templates/SALES_BM_TEMPLATE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
   <si>
     <t>Date</t>
   </si>
@@ -84,6 +84,18 @@
   </si>
   <si>
     <t>Postage Loss</t>
+  </si>
+  <si>
+    <t>Fees Kept</t>
+  </si>
+  <si>
+    <t>Repair Cost</t>
+  </si>
+  <si>
+    <t>Supplier Credit</t>
+  </si>
+  <si>
+    <t>Return Cost</t>
   </si>
   <si>
     <t>Net GP £</t>
@@ -586,74 +598,74 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" t="s">
         <v>37</v>
-      </c>
-      <c r="B1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -664,10 +676,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD203"/>
+  <dimension ref="A1:AH203"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -758,37 +770,49 @@
       <c r="AD1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46235.5</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K2" s="3">
         <v>240</v>
@@ -809,7 +833,7 @@
         <v>8.99</v>
       </c>
       <c r="Q2" s="3">
-        <f>L2*1%</f>
+        <v>0</v>
       </c>
       <c r="R2" s="3">
         <v>8</v>
@@ -824,19 +848,19 @@
         <f>M2-N2-O2-P2-Q2-R2-S2-T2</f>
       </c>
       <c r="V2" s="3">
-        <f>(U2-X2)/K2*100</f>
+        <f>(U2-AB2)/K2*100</f>
       </c>
       <c r="W2" s="3">
         <f>N2-S2</f>
       </c>
-      <c r="Y2" s="3">
-        <f>U2-X2</f>
-      </c>
-      <c r="AD2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC2" s="3">
+        <f>U2-AB2</f>
+      </c>
+      <c r="AH2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="D3" s="2"/>
       <c r="K3" s="3"/>
@@ -867,16 +891,16 @@
         <f>IF($L3="","",M3-N3-O3-P3-Q3-R3-S3-T3)</f>
       </c>
       <c r="V3" s="3">
-        <f>IF($L3="","",(U3-X3)/K3*100)</f>
+        <f>IF($L3="","",(U3-AB3)/K3*100)</f>
       </c>
       <c r="W3" s="3">
         <f>IF($L3="","",N3-S3)</f>
       </c>
-      <c r="Y3" s="3">
-        <f>IF($L3="","",U3-X3)</f>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC3" s="3">
+        <f>IF($L3="","",U3-AB3)</f>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="D4" s="2"/>
       <c r="K4" s="3"/>
@@ -907,16 +931,16 @@
         <f>IF($L4="","",M4-N4-O4-P4-Q4-R4-S4-T4)</f>
       </c>
       <c r="V4" s="3">
-        <f>IF($L4="","",(U4-X4)/K4*100)</f>
+        <f>IF($L4="","",(U4-AB4)/K4*100)</f>
       </c>
       <c r="W4" s="3">
         <f>IF($L4="","",N4-S4)</f>
       </c>
-      <c r="Y4" s="3">
-        <f>IF($L4="","",U4-X4)</f>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC4" s="3">
+        <f>IF($L4="","",U4-AB4)</f>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="D5" s="2"/>
       <c r="K5" s="3"/>
@@ -947,16 +971,16 @@
         <f>IF($L5="","",M5-N5-O5-P5-Q5-R5-S5-T5)</f>
       </c>
       <c r="V5" s="3">
-        <f>IF($L5="","",(U5-X5)/K5*100)</f>
+        <f>IF($L5="","",(U5-AB5)/K5*100)</f>
       </c>
       <c r="W5" s="3">
         <f>IF($L5="","",N5-S5)</f>
       </c>
-      <c r="Y5" s="3">
-        <f>IF($L5="","",U5-X5)</f>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC5" s="3">
+        <f>IF($L5="","",U5-AB5)</f>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="D6" s="2"/>
       <c r="K6" s="3"/>
@@ -987,16 +1011,16 @@
         <f>IF($L6="","",M6-N6-O6-P6-Q6-R6-S6-T6)</f>
       </c>
       <c r="V6" s="3">
-        <f>IF($L6="","",(U6-X6)/K6*100)</f>
+        <f>IF($L6="","",(U6-AB6)/K6*100)</f>
       </c>
       <c r="W6" s="3">
         <f>IF($L6="","",N6-S6)</f>
       </c>
-      <c r="Y6" s="3">
-        <f>IF($L6="","",U6-X6)</f>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC6" s="3">
+        <f>IF($L6="","",U6-AB6)</f>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="D7" s="2"/>
       <c r="K7" s="3"/>
@@ -1027,16 +1051,16 @@
         <f>IF($L7="","",M7-N7-O7-P7-Q7-R7-S7-T7)</f>
       </c>
       <c r="V7" s="3">
-        <f>IF($L7="","",(U7-X7)/K7*100)</f>
+        <f>IF($L7="","",(U7-AB7)/K7*100)</f>
       </c>
       <c r="W7" s="3">
         <f>IF($L7="","",N7-S7)</f>
       </c>
-      <c r="Y7" s="3">
-        <f>IF($L7="","",U7-X7)</f>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC7" s="3">
+        <f>IF($L7="","",U7-AB7)</f>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="D8" s="2"/>
       <c r="K8" s="3"/>
@@ -1067,16 +1091,16 @@
         <f>IF($L8="","",M8-N8-O8-P8-Q8-R8-S8-T8)</f>
       </c>
       <c r="V8" s="3">
-        <f>IF($L8="","",(U8-X8)/K8*100)</f>
+        <f>IF($L8="","",(U8-AB8)/K8*100)</f>
       </c>
       <c r="W8" s="3">
         <f>IF($L8="","",N8-S8)</f>
       </c>
-      <c r="Y8" s="3">
-        <f>IF($L8="","",U8-X8)</f>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC8" s="3">
+        <f>IF($L8="","",U8-AB8)</f>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="D9" s="2"/>
       <c r="K9" s="3"/>
@@ -1107,16 +1131,16 @@
         <f>IF($L9="","",M9-N9-O9-P9-Q9-R9-S9-T9)</f>
       </c>
       <c r="V9" s="3">
-        <f>IF($L9="","",(U9-X9)/K9*100)</f>
+        <f>IF($L9="","",(U9-AB9)/K9*100)</f>
       </c>
       <c r="W9" s="3">
         <f>IF($L9="","",N9-S9)</f>
       </c>
-      <c r="Y9" s="3">
-        <f>IF($L9="","",U9-X9)</f>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC9" s="3">
+        <f>IF($L9="","",U9-AB9)</f>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="D10" s="2"/>
       <c r="K10" s="3"/>
@@ -1147,16 +1171,16 @@
         <f>IF($L10="","",M10-N10-O10-P10-Q10-R10-S10-T10)</f>
       </c>
       <c r="V10" s="3">
-        <f>IF($L10="","",(U10-X10)/K10*100)</f>
+        <f>IF($L10="","",(U10-AB10)/K10*100)</f>
       </c>
       <c r="W10" s="3">
         <f>IF($L10="","",N10-S10)</f>
       </c>
-      <c r="Y10" s="3">
-        <f>IF($L10="","",U10-X10)</f>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC10" s="3">
+        <f>IF($L10="","",U10-AB10)</f>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="D11" s="2"/>
       <c r="K11" s="3"/>
@@ -1187,16 +1211,16 @@
         <f>IF($L11="","",M11-N11-O11-P11-Q11-R11-S11-T11)</f>
       </c>
       <c r="V11" s="3">
-        <f>IF($L11="","",(U11-X11)/K11*100)</f>
+        <f>IF($L11="","",(U11-AB11)/K11*100)</f>
       </c>
       <c r="W11" s="3">
         <f>IF($L11="","",N11-S11)</f>
       </c>
-      <c r="Y11" s="3">
-        <f>IF($L11="","",U11-X11)</f>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC11" s="3">
+        <f>IF($L11="","",U11-AB11)</f>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="D12" s="2"/>
       <c r="K12" s="3"/>
@@ -1227,16 +1251,16 @@
         <f>IF($L12="","",M12-N12-O12-P12-Q12-R12-S12-T12)</f>
       </c>
       <c r="V12" s="3">
-        <f>IF($L12="","",(U12-X12)/K12*100)</f>
+        <f>IF($L12="","",(U12-AB12)/K12*100)</f>
       </c>
       <c r="W12" s="3">
         <f>IF($L12="","",N12-S12)</f>
       </c>
-      <c r="Y12" s="3">
-        <f>IF($L12="","",U12-X12)</f>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC12" s="3">
+        <f>IF($L12="","",U12-AB12)</f>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="D13" s="2"/>
       <c r="K13" s="3"/>
@@ -1267,16 +1291,16 @@
         <f>IF($L13="","",M13-N13-O13-P13-Q13-R13-S13-T13)</f>
       </c>
       <c r="V13" s="3">
-        <f>IF($L13="","",(U13-X13)/K13*100)</f>
+        <f>IF($L13="","",(U13-AB13)/K13*100)</f>
       </c>
       <c r="W13" s="3">
         <f>IF($L13="","",N13-S13)</f>
       </c>
-      <c r="Y13" s="3">
-        <f>IF($L13="","",U13-X13)</f>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC13" s="3">
+        <f>IF($L13="","",U13-AB13)</f>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="2"/>
       <c r="K14" s="3"/>
@@ -1307,16 +1331,16 @@
         <f>IF($L14="","",M14-N14-O14-P14-Q14-R14-S14-T14)</f>
       </c>
       <c r="V14" s="3">
-        <f>IF($L14="","",(U14-X14)/K14*100)</f>
+        <f>IF($L14="","",(U14-AB14)/K14*100)</f>
       </c>
       <c r="W14" s="3">
         <f>IF($L14="","",N14-S14)</f>
       </c>
-      <c r="Y14" s="3">
-        <f>IF($L14="","",U14-X14)</f>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC14" s="3">
+        <f>IF($L14="","",U14-AB14)</f>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="D15" s="2"/>
       <c r="K15" s="3"/>
@@ -1347,16 +1371,16 @@
         <f>IF($L15="","",M15-N15-O15-P15-Q15-R15-S15-T15)</f>
       </c>
       <c r="V15" s="3">
-        <f>IF($L15="","",(U15-X15)/K15*100)</f>
+        <f>IF($L15="","",(U15-AB15)/K15*100)</f>
       </c>
       <c r="W15" s="3">
         <f>IF($L15="","",N15-S15)</f>
       </c>
-      <c r="Y15" s="3">
-        <f>IF($L15="","",U15-X15)</f>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC15" s="3">
+        <f>IF($L15="","",U15-AB15)</f>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="D16" s="2"/>
       <c r="K16" s="3"/>
@@ -1387,16 +1411,16 @@
         <f>IF($L16="","",M16-N16-O16-P16-Q16-R16-S16-T16)</f>
       </c>
       <c r="V16" s="3">
-        <f>IF($L16="","",(U16-X16)/K16*100)</f>
+        <f>IF($L16="","",(U16-AB16)/K16*100)</f>
       </c>
       <c r="W16" s="3">
         <f>IF($L16="","",N16-S16)</f>
       </c>
-      <c r="Y16" s="3">
-        <f>IF($L16="","",U16-X16)</f>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC16" s="3">
+        <f>IF($L16="","",U16-AB16)</f>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="D17" s="2"/>
       <c r="K17" s="3"/>
@@ -1427,16 +1451,16 @@
         <f>IF($L17="","",M17-N17-O17-P17-Q17-R17-S17-T17)</f>
       </c>
       <c r="V17" s="3">
-        <f>IF($L17="","",(U17-X17)/K17*100)</f>
+        <f>IF($L17="","",(U17-AB17)/K17*100)</f>
       </c>
       <c r="W17" s="3">
         <f>IF($L17="","",N17-S17)</f>
       </c>
-      <c r="Y17" s="3">
-        <f>IF($L17="","",U17-X17)</f>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC17" s="3">
+        <f>IF($L17="","",U17-AB17)</f>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="D18" s="2"/>
       <c r="K18" s="3"/>
@@ -1467,16 +1491,16 @@
         <f>IF($L18="","",M18-N18-O18-P18-Q18-R18-S18-T18)</f>
       </c>
       <c r="V18" s="3">
-        <f>IF($L18="","",(U18-X18)/K18*100)</f>
+        <f>IF($L18="","",(U18-AB18)/K18*100)</f>
       </c>
       <c r="W18" s="3">
         <f>IF($L18="","",N18-S18)</f>
       </c>
-      <c r="Y18" s="3">
-        <f>IF($L18="","",U18-X18)</f>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC18" s="3">
+        <f>IF($L18="","",U18-AB18)</f>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="D19" s="2"/>
       <c r="K19" s="3"/>
@@ -1507,16 +1531,16 @@
         <f>IF($L19="","",M19-N19-O19-P19-Q19-R19-S19-T19)</f>
       </c>
       <c r="V19" s="3">
-        <f>IF($L19="","",(U19-X19)/K19*100)</f>
+        <f>IF($L19="","",(U19-AB19)/K19*100)</f>
       </c>
       <c r="W19" s="3">
         <f>IF($L19="","",N19-S19)</f>
       </c>
-      <c r="Y19" s="3">
-        <f>IF($L19="","",U19-X19)</f>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC19" s="3">
+        <f>IF($L19="","",U19-AB19)</f>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="D20" s="2"/>
       <c r="K20" s="3"/>
@@ -1547,16 +1571,16 @@
         <f>IF($L20="","",M20-N20-O20-P20-Q20-R20-S20-T20)</f>
       </c>
       <c r="V20" s="3">
-        <f>IF($L20="","",(U20-X20)/K20*100)</f>
+        <f>IF($L20="","",(U20-AB20)/K20*100)</f>
       </c>
       <c r="W20" s="3">
         <f>IF($L20="","",N20-S20)</f>
       </c>
-      <c r="Y20" s="3">
-        <f>IF($L20="","",U20-X20)</f>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC20" s="3">
+        <f>IF($L20="","",U20-AB20)</f>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="D21" s="2"/>
       <c r="K21" s="3"/>
@@ -1587,16 +1611,16 @@
         <f>IF($L21="","",M21-N21-O21-P21-Q21-R21-S21-T21)</f>
       </c>
       <c r="V21" s="3">
-        <f>IF($L21="","",(U21-X21)/K21*100)</f>
+        <f>IF($L21="","",(U21-AB21)/K21*100)</f>
       </c>
       <c r="W21" s="3">
         <f>IF($L21="","",N21-S21)</f>
       </c>
-      <c r="Y21" s="3">
-        <f>IF($L21="","",U21-X21)</f>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC21" s="3">
+        <f>IF($L21="","",U21-AB21)</f>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="D22" s="2"/>
       <c r="K22" s="3"/>
@@ -1627,16 +1651,16 @@
         <f>IF($L22="","",M22-N22-O22-P22-Q22-R22-S22-T22)</f>
       </c>
       <c r="V22" s="3">
-        <f>IF($L22="","",(U22-X22)/K22*100)</f>
+        <f>IF($L22="","",(U22-AB22)/K22*100)</f>
       </c>
       <c r="W22" s="3">
         <f>IF($L22="","",N22-S22)</f>
       </c>
-      <c r="Y22" s="3">
-        <f>IF($L22="","",U22-X22)</f>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC22" s="3">
+        <f>IF($L22="","",U22-AB22)</f>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="D23" s="2"/>
       <c r="K23" s="3"/>
@@ -1667,16 +1691,16 @@
         <f>IF($L23="","",M23-N23-O23-P23-Q23-R23-S23-T23)</f>
       </c>
       <c r="V23" s="3">
-        <f>IF($L23="","",(U23-X23)/K23*100)</f>
+        <f>IF($L23="","",(U23-AB23)/K23*100)</f>
       </c>
       <c r="W23" s="3">
         <f>IF($L23="","",N23-S23)</f>
       </c>
-      <c r="Y23" s="3">
-        <f>IF($L23="","",U23-X23)</f>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC23" s="3">
+        <f>IF($L23="","",U23-AB23)</f>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="D24" s="2"/>
       <c r="K24" s="3"/>
@@ -1707,16 +1731,16 @@
         <f>IF($L24="","",M24-N24-O24-P24-Q24-R24-S24-T24)</f>
       </c>
       <c r="V24" s="3">
-        <f>IF($L24="","",(U24-X24)/K24*100)</f>
+        <f>IF($L24="","",(U24-AB24)/K24*100)</f>
       </c>
       <c r="W24" s="3">
         <f>IF($L24="","",N24-S24)</f>
       </c>
-      <c r="Y24" s="3">
-        <f>IF($L24="","",U24-X24)</f>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC24" s="3">
+        <f>IF($L24="","",U24-AB24)</f>
+      </c>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="D25" s="2"/>
       <c r="K25" s="3"/>
@@ -1747,16 +1771,16 @@
         <f>IF($L25="","",M25-N25-O25-P25-Q25-R25-S25-T25)</f>
       </c>
       <c r="V25" s="3">
-        <f>IF($L25="","",(U25-X25)/K25*100)</f>
+        <f>IF($L25="","",(U25-AB25)/K25*100)</f>
       </c>
       <c r="W25" s="3">
         <f>IF($L25="","",N25-S25)</f>
       </c>
-      <c r="Y25" s="3">
-        <f>IF($L25="","",U25-X25)</f>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC25" s="3">
+        <f>IF($L25="","",U25-AB25)</f>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="D26" s="2"/>
       <c r="K26" s="3"/>
@@ -1787,16 +1811,16 @@
         <f>IF($L26="","",M26-N26-O26-P26-Q26-R26-S26-T26)</f>
       </c>
       <c r="V26" s="3">
-        <f>IF($L26="","",(U26-X26)/K26*100)</f>
+        <f>IF($L26="","",(U26-AB26)/K26*100)</f>
       </c>
       <c r="W26" s="3">
         <f>IF($L26="","",N26-S26)</f>
       </c>
-      <c r="Y26" s="3">
-        <f>IF($L26="","",U26-X26)</f>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC26" s="3">
+        <f>IF($L26="","",U26-AB26)</f>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="D27" s="2"/>
       <c r="K27" s="3"/>
@@ -1827,16 +1851,16 @@
         <f>IF($L27="","",M27-N27-O27-P27-Q27-R27-S27-T27)</f>
       </c>
       <c r="V27" s="3">
-        <f>IF($L27="","",(U27-X27)/K27*100)</f>
+        <f>IF($L27="","",(U27-AB27)/K27*100)</f>
       </c>
       <c r="W27" s="3">
         <f>IF($L27="","",N27-S27)</f>
       </c>
-      <c r="Y27" s="3">
-        <f>IF($L27="","",U27-X27)</f>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC27" s="3">
+        <f>IF($L27="","",U27-AB27)</f>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="D28" s="2"/>
       <c r="K28" s="3"/>
@@ -1867,16 +1891,16 @@
         <f>IF($L28="","",M28-N28-O28-P28-Q28-R28-S28-T28)</f>
       </c>
       <c r="V28" s="3">
-        <f>IF($L28="","",(U28-X28)/K28*100)</f>
+        <f>IF($L28="","",(U28-AB28)/K28*100)</f>
       </c>
       <c r="W28" s="3">
         <f>IF($L28="","",N28-S28)</f>
       </c>
-      <c r="Y28" s="3">
-        <f>IF($L28="","",U28-X28)</f>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC28" s="3">
+        <f>IF($L28="","",U28-AB28)</f>
+      </c>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="D29" s="2"/>
       <c r="K29" s="3"/>
@@ -1907,16 +1931,16 @@
         <f>IF($L29="","",M29-N29-O29-P29-Q29-R29-S29-T29)</f>
       </c>
       <c r="V29" s="3">
-        <f>IF($L29="","",(U29-X29)/K29*100)</f>
+        <f>IF($L29="","",(U29-AB29)/K29*100)</f>
       </c>
       <c r="W29" s="3">
         <f>IF($L29="","",N29-S29)</f>
       </c>
-      <c r="Y29" s="3">
-        <f>IF($L29="","",U29-X29)</f>
-      </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC29" s="3">
+        <f>IF($L29="","",U29-AB29)</f>
+      </c>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="D30" s="2"/>
       <c r="K30" s="3"/>
@@ -1947,16 +1971,16 @@
         <f>IF($L30="","",M30-N30-O30-P30-Q30-R30-S30-T30)</f>
       </c>
       <c r="V30" s="3">
-        <f>IF($L30="","",(U30-X30)/K30*100)</f>
+        <f>IF($L30="","",(U30-AB30)/K30*100)</f>
       </c>
       <c r="W30" s="3">
         <f>IF($L30="","",N30-S30)</f>
       </c>
-      <c r="Y30" s="3">
-        <f>IF($L30="","",U30-X30)</f>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC30" s="3">
+        <f>IF($L30="","",U30-AB30)</f>
+      </c>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="D31" s="2"/>
       <c r="K31" s="3"/>
@@ -1987,16 +2011,16 @@
         <f>IF($L31="","",M31-N31-O31-P31-Q31-R31-S31-T31)</f>
       </c>
       <c r="V31" s="3">
-        <f>IF($L31="","",(U31-X31)/K31*100)</f>
+        <f>IF($L31="","",(U31-AB31)/K31*100)</f>
       </c>
       <c r="W31" s="3">
         <f>IF($L31="","",N31-S31)</f>
       </c>
-      <c r="Y31" s="3">
-        <f>IF($L31="","",U31-X31)</f>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC31" s="3">
+        <f>IF($L31="","",U31-AB31)</f>
+      </c>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="D32" s="2"/>
       <c r="K32" s="3"/>
@@ -2027,16 +2051,16 @@
         <f>IF($L32="","",M32-N32-O32-P32-Q32-R32-S32-T32)</f>
       </c>
       <c r="V32" s="3">
-        <f>IF($L32="","",(U32-X32)/K32*100)</f>
+        <f>IF($L32="","",(U32-AB32)/K32*100)</f>
       </c>
       <c r="W32" s="3">
         <f>IF($L32="","",N32-S32)</f>
       </c>
-      <c r="Y32" s="3">
-        <f>IF($L32="","",U32-X32)</f>
-      </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC32" s="3">
+        <f>IF($L32="","",U32-AB32)</f>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="D33" s="2"/>
       <c r="K33" s="3"/>
@@ -2067,16 +2091,16 @@
         <f>IF($L33="","",M33-N33-O33-P33-Q33-R33-S33-T33)</f>
       </c>
       <c r="V33" s="3">
-        <f>IF($L33="","",(U33-X33)/K33*100)</f>
+        <f>IF($L33="","",(U33-AB33)/K33*100)</f>
       </c>
       <c r="W33" s="3">
         <f>IF($L33="","",N33-S33)</f>
       </c>
-      <c r="Y33" s="3">
-        <f>IF($L33="","",U33-X33)</f>
-      </c>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC33" s="3">
+        <f>IF($L33="","",U33-AB33)</f>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="D34" s="2"/>
       <c r="K34" s="3"/>
@@ -2107,16 +2131,16 @@
         <f>IF($L34="","",M34-N34-O34-P34-Q34-R34-S34-T34)</f>
       </c>
       <c r="V34" s="3">
-        <f>IF($L34="","",(U34-X34)/K34*100)</f>
+        <f>IF($L34="","",(U34-AB34)/K34*100)</f>
       </c>
       <c r="W34" s="3">
         <f>IF($L34="","",N34-S34)</f>
       </c>
-      <c r="Y34" s="3">
-        <f>IF($L34="","",U34-X34)</f>
-      </c>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC34" s="3">
+        <f>IF($L34="","",U34-AB34)</f>
+      </c>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="D35" s="2"/>
       <c r="K35" s="3"/>
@@ -2147,16 +2171,16 @@
         <f>IF($L35="","",M35-N35-O35-P35-Q35-R35-S35-T35)</f>
       </c>
       <c r="V35" s="3">
-        <f>IF($L35="","",(U35-X35)/K35*100)</f>
+        <f>IF($L35="","",(U35-AB35)/K35*100)</f>
       </c>
       <c r="W35" s="3">
         <f>IF($L35="","",N35-S35)</f>
       </c>
-      <c r="Y35" s="3">
-        <f>IF($L35="","",U35-X35)</f>
-      </c>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC35" s="3">
+        <f>IF($L35="","",U35-AB35)</f>
+      </c>
+    </row>
+    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="D36" s="2"/>
       <c r="K36" s="3"/>
@@ -2187,16 +2211,16 @@
         <f>IF($L36="","",M36-N36-O36-P36-Q36-R36-S36-T36)</f>
       </c>
       <c r="V36" s="3">
-        <f>IF($L36="","",(U36-X36)/K36*100)</f>
+        <f>IF($L36="","",(U36-AB36)/K36*100)</f>
       </c>
       <c r="W36" s="3">
         <f>IF($L36="","",N36-S36)</f>
       </c>
-      <c r="Y36" s="3">
-        <f>IF($L36="","",U36-X36)</f>
-      </c>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC36" s="3">
+        <f>IF($L36="","",U36-AB36)</f>
+      </c>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="D37" s="2"/>
       <c r="K37" s="3"/>
@@ -2227,16 +2251,16 @@
         <f>IF($L37="","",M37-N37-O37-P37-Q37-R37-S37-T37)</f>
       </c>
       <c r="V37" s="3">
-        <f>IF($L37="","",(U37-X37)/K37*100)</f>
+        <f>IF($L37="","",(U37-AB37)/K37*100)</f>
       </c>
       <c r="W37" s="3">
         <f>IF($L37="","",N37-S37)</f>
       </c>
-      <c r="Y37" s="3">
-        <f>IF($L37="","",U37-X37)</f>
-      </c>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC37" s="3">
+        <f>IF($L37="","",U37-AB37)</f>
+      </c>
+    </row>
+    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="D38" s="2"/>
       <c r="K38" s="3"/>
@@ -2267,16 +2291,16 @@
         <f>IF($L38="","",M38-N38-O38-P38-Q38-R38-S38-T38)</f>
       </c>
       <c r="V38" s="3">
-        <f>IF($L38="","",(U38-X38)/K38*100)</f>
+        <f>IF($L38="","",(U38-AB38)/K38*100)</f>
       </c>
       <c r="W38" s="3">
         <f>IF($L38="","",N38-S38)</f>
       </c>
-      <c r="Y38" s="3">
-        <f>IF($L38="","",U38-X38)</f>
-      </c>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC38" s="3">
+        <f>IF($L38="","",U38-AB38)</f>
+      </c>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="D39" s="2"/>
       <c r="K39" s="3"/>
@@ -2307,16 +2331,16 @@
         <f>IF($L39="","",M39-N39-O39-P39-Q39-R39-S39-T39)</f>
       </c>
       <c r="V39" s="3">
-        <f>IF($L39="","",(U39-X39)/K39*100)</f>
+        <f>IF($L39="","",(U39-AB39)/K39*100)</f>
       </c>
       <c r="W39" s="3">
         <f>IF($L39="","",N39-S39)</f>
       </c>
-      <c r="Y39" s="3">
-        <f>IF($L39="","",U39-X39)</f>
-      </c>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC39" s="3">
+        <f>IF($L39="","",U39-AB39)</f>
+      </c>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="D40" s="2"/>
       <c r="K40" s="3"/>
@@ -2347,16 +2371,16 @@
         <f>IF($L40="","",M40-N40-O40-P40-Q40-R40-S40-T40)</f>
       </c>
       <c r="V40" s="3">
-        <f>IF($L40="","",(U40-X40)/K40*100)</f>
+        <f>IF($L40="","",(U40-AB40)/K40*100)</f>
       </c>
       <c r="W40" s="3">
         <f>IF($L40="","",N40-S40)</f>
       </c>
-      <c r="Y40" s="3">
-        <f>IF($L40="","",U40-X40)</f>
-      </c>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC40" s="3">
+        <f>IF($L40="","",U40-AB40)</f>
+      </c>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="D41" s="2"/>
       <c r="K41" s="3"/>
@@ -2387,16 +2411,16 @@
         <f>IF($L41="","",M41-N41-O41-P41-Q41-R41-S41-T41)</f>
       </c>
       <c r="V41" s="3">
-        <f>IF($L41="","",(U41-X41)/K41*100)</f>
+        <f>IF($L41="","",(U41-AB41)/K41*100)</f>
       </c>
       <c r="W41" s="3">
         <f>IF($L41="","",N41-S41)</f>
       </c>
-      <c r="Y41" s="3">
-        <f>IF($L41="","",U41-X41)</f>
-      </c>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC41" s="3">
+        <f>IF($L41="","",U41-AB41)</f>
+      </c>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="D42" s="2"/>
       <c r="K42" s="3"/>
@@ -2427,16 +2451,16 @@
         <f>IF($L42="","",M42-N42-O42-P42-Q42-R42-S42-T42)</f>
       </c>
       <c r="V42" s="3">
-        <f>IF($L42="","",(U42-X42)/K42*100)</f>
+        <f>IF($L42="","",(U42-AB42)/K42*100)</f>
       </c>
       <c r="W42" s="3">
         <f>IF($L42="","",N42-S42)</f>
       </c>
-      <c r="Y42" s="3">
-        <f>IF($L42="","",U42-X42)</f>
-      </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC42" s="3">
+        <f>IF($L42="","",U42-AB42)</f>
+      </c>
+    </row>
+    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="D43" s="2"/>
       <c r="K43" s="3"/>
@@ -2467,16 +2491,16 @@
         <f>IF($L43="","",M43-N43-O43-P43-Q43-R43-S43-T43)</f>
       </c>
       <c r="V43" s="3">
-        <f>IF($L43="","",(U43-X43)/K43*100)</f>
+        <f>IF($L43="","",(U43-AB43)/K43*100)</f>
       </c>
       <c r="W43" s="3">
         <f>IF($L43="","",N43-S43)</f>
       </c>
-      <c r="Y43" s="3">
-        <f>IF($L43="","",U43-X43)</f>
-      </c>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC43" s="3">
+        <f>IF($L43="","",U43-AB43)</f>
+      </c>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="D44" s="2"/>
       <c r="K44" s="3"/>
@@ -2507,16 +2531,16 @@
         <f>IF($L44="","",M44-N44-O44-P44-Q44-R44-S44-T44)</f>
       </c>
       <c r="V44" s="3">
-        <f>IF($L44="","",(U44-X44)/K44*100)</f>
+        <f>IF($L44="","",(U44-AB44)/K44*100)</f>
       </c>
       <c r="W44" s="3">
         <f>IF($L44="","",N44-S44)</f>
       </c>
-      <c r="Y44" s="3">
-        <f>IF($L44="","",U44-X44)</f>
-      </c>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC44" s="3">
+        <f>IF($L44="","",U44-AB44)</f>
+      </c>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="D45" s="2"/>
       <c r="K45" s="3"/>
@@ -2547,16 +2571,16 @@
         <f>IF($L45="","",M45-N45-O45-P45-Q45-R45-S45-T45)</f>
       </c>
       <c r="V45" s="3">
-        <f>IF($L45="","",(U45-X45)/K45*100)</f>
+        <f>IF($L45="","",(U45-AB45)/K45*100)</f>
       </c>
       <c r="W45" s="3">
         <f>IF($L45="","",N45-S45)</f>
       </c>
-      <c r="Y45" s="3">
-        <f>IF($L45="","",U45-X45)</f>
-      </c>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC45" s="3">
+        <f>IF($L45="","",U45-AB45)</f>
+      </c>
+    </row>
+    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="D46" s="2"/>
       <c r="K46" s="3"/>
@@ -2587,16 +2611,16 @@
         <f>IF($L46="","",M46-N46-O46-P46-Q46-R46-S46-T46)</f>
       </c>
       <c r="V46" s="3">
-        <f>IF($L46="","",(U46-X46)/K46*100)</f>
+        <f>IF($L46="","",(U46-AB46)/K46*100)</f>
       </c>
       <c r="W46" s="3">
         <f>IF($L46="","",N46-S46)</f>
       </c>
-      <c r="Y46" s="3">
-        <f>IF($L46="","",U46-X46)</f>
-      </c>
-    </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC46" s="3">
+        <f>IF($L46="","",U46-AB46)</f>
+      </c>
+    </row>
+    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="D47" s="2"/>
       <c r="K47" s="3"/>
@@ -2627,16 +2651,16 @@
         <f>IF($L47="","",M47-N47-O47-P47-Q47-R47-S47-T47)</f>
       </c>
       <c r="V47" s="3">
-        <f>IF($L47="","",(U47-X47)/K47*100)</f>
+        <f>IF($L47="","",(U47-AB47)/K47*100)</f>
       </c>
       <c r="W47" s="3">
         <f>IF($L47="","",N47-S47)</f>
       </c>
-      <c r="Y47" s="3">
-        <f>IF($L47="","",U47-X47)</f>
-      </c>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC47" s="3">
+        <f>IF($L47="","",U47-AB47)</f>
+      </c>
+    </row>
+    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="D48" s="2"/>
       <c r="K48" s="3"/>
@@ -2667,16 +2691,16 @@
         <f>IF($L48="","",M48-N48-O48-P48-Q48-R48-S48-T48)</f>
       </c>
       <c r="V48" s="3">
-        <f>IF($L48="","",(U48-X48)/K48*100)</f>
+        <f>IF($L48="","",(U48-AB48)/K48*100)</f>
       </c>
       <c r="W48" s="3">
         <f>IF($L48="","",N48-S48)</f>
       </c>
-      <c r="Y48" s="3">
-        <f>IF($L48="","",U48-X48)</f>
-      </c>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC48" s="3">
+        <f>IF($L48="","",U48-AB48)</f>
+      </c>
+    </row>
+    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="D49" s="2"/>
       <c r="K49" s="3"/>
@@ -2707,16 +2731,16 @@
         <f>IF($L49="","",M49-N49-O49-P49-Q49-R49-S49-T49)</f>
       </c>
       <c r="V49" s="3">
-        <f>IF($L49="","",(U49-X49)/K49*100)</f>
+        <f>IF($L49="","",(U49-AB49)/K49*100)</f>
       </c>
       <c r="W49" s="3">
         <f>IF($L49="","",N49-S49)</f>
       </c>
-      <c r="Y49" s="3">
-        <f>IF($L49="","",U49-X49)</f>
-      </c>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC49" s="3">
+        <f>IF($L49="","",U49-AB49)</f>
+      </c>
+    </row>
+    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="D50" s="2"/>
       <c r="K50" s="3"/>
@@ -2747,16 +2771,16 @@
         <f>IF($L50="","",M50-N50-O50-P50-Q50-R50-S50-T50)</f>
       </c>
       <c r="V50" s="3">
-        <f>IF($L50="","",(U50-X50)/K50*100)</f>
+        <f>IF($L50="","",(U50-AB50)/K50*100)</f>
       </c>
       <c r="W50" s="3">
         <f>IF($L50="","",N50-S50)</f>
       </c>
-      <c r="Y50" s="3">
-        <f>IF($L50="","",U50-X50)</f>
-      </c>
-    </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC50" s="3">
+        <f>IF($L50="","",U50-AB50)</f>
+      </c>
+    </row>
+    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="D51" s="2"/>
       <c r="K51" s="3"/>
@@ -2787,16 +2811,16 @@
         <f>IF($L51="","",M51-N51-O51-P51-Q51-R51-S51-T51)</f>
       </c>
       <c r="V51" s="3">
-        <f>IF($L51="","",(U51-X51)/K51*100)</f>
+        <f>IF($L51="","",(U51-AB51)/K51*100)</f>
       </c>
       <c r="W51" s="3">
         <f>IF($L51="","",N51-S51)</f>
       </c>
-      <c r="Y51" s="3">
-        <f>IF($L51="","",U51-X51)</f>
-      </c>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC51" s="3">
+        <f>IF($L51="","",U51-AB51)</f>
+      </c>
+    </row>
+    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="D52" s="2"/>
       <c r="K52" s="3"/>
@@ -2827,16 +2851,16 @@
         <f>IF($L52="","",M52-N52-O52-P52-Q52-R52-S52-T52)</f>
       </c>
       <c r="V52" s="3">
-        <f>IF($L52="","",(U52-X52)/K52*100)</f>
+        <f>IF($L52="","",(U52-AB52)/K52*100)</f>
       </c>
       <c r="W52" s="3">
         <f>IF($L52="","",N52-S52)</f>
       </c>
-      <c r="Y52" s="3">
-        <f>IF($L52="","",U52-X52)</f>
-      </c>
-    </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC52" s="3">
+        <f>IF($L52="","",U52-AB52)</f>
+      </c>
+    </row>
+    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="D53" s="2"/>
       <c r="K53" s="3"/>
@@ -2867,16 +2891,16 @@
         <f>IF($L53="","",M53-N53-O53-P53-Q53-R53-S53-T53)</f>
       </c>
       <c r="V53" s="3">
-        <f>IF($L53="","",(U53-X53)/K53*100)</f>
+        <f>IF($L53="","",(U53-AB53)/K53*100)</f>
       </c>
       <c r="W53" s="3">
         <f>IF($L53="","",N53-S53)</f>
       </c>
-      <c r="Y53" s="3">
-        <f>IF($L53="","",U53-X53)</f>
-      </c>
-    </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC53" s="3">
+        <f>IF($L53="","",U53-AB53)</f>
+      </c>
+    </row>
+    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="D54" s="2"/>
       <c r="K54" s="3"/>
@@ -2907,16 +2931,16 @@
         <f>IF($L54="","",M54-N54-O54-P54-Q54-R54-S54-T54)</f>
       </c>
       <c r="V54" s="3">
-        <f>IF($L54="","",(U54-X54)/K54*100)</f>
+        <f>IF($L54="","",(U54-AB54)/K54*100)</f>
       </c>
       <c r="W54" s="3">
         <f>IF($L54="","",N54-S54)</f>
       </c>
-      <c r="Y54" s="3">
-        <f>IF($L54="","",U54-X54)</f>
-      </c>
-    </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC54" s="3">
+        <f>IF($L54="","",U54-AB54)</f>
+      </c>
+    </row>
+    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="D55" s="2"/>
       <c r="K55" s="3"/>
@@ -2947,16 +2971,16 @@
         <f>IF($L55="","",M55-N55-O55-P55-Q55-R55-S55-T55)</f>
       </c>
       <c r="V55" s="3">
-        <f>IF($L55="","",(U55-X55)/K55*100)</f>
+        <f>IF($L55="","",(U55-AB55)/K55*100)</f>
       </c>
       <c r="W55" s="3">
         <f>IF($L55="","",N55-S55)</f>
       </c>
-      <c r="Y55" s="3">
-        <f>IF($L55="","",U55-X55)</f>
-      </c>
-    </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC55" s="3">
+        <f>IF($L55="","",U55-AB55)</f>
+      </c>
+    </row>
+    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="D56" s="2"/>
       <c r="K56" s="3"/>
@@ -2987,16 +3011,16 @@
         <f>IF($L56="","",M56-N56-O56-P56-Q56-R56-S56-T56)</f>
       </c>
       <c r="V56" s="3">
-        <f>IF($L56="","",(U56-X56)/K56*100)</f>
+        <f>IF($L56="","",(U56-AB56)/K56*100)</f>
       </c>
       <c r="W56" s="3">
         <f>IF($L56="","",N56-S56)</f>
       </c>
-      <c r="Y56" s="3">
-        <f>IF($L56="","",U56-X56)</f>
-      </c>
-    </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC56" s="3">
+        <f>IF($L56="","",U56-AB56)</f>
+      </c>
+    </row>
+    <row r="57" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="D57" s="2"/>
       <c r="K57" s="3"/>
@@ -3027,16 +3051,16 @@
         <f>IF($L57="","",M57-N57-O57-P57-Q57-R57-S57-T57)</f>
       </c>
       <c r="V57" s="3">
-        <f>IF($L57="","",(U57-X57)/K57*100)</f>
+        <f>IF($L57="","",(U57-AB57)/K57*100)</f>
       </c>
       <c r="W57" s="3">
         <f>IF($L57="","",N57-S57)</f>
       </c>
-      <c r="Y57" s="3">
-        <f>IF($L57="","",U57-X57)</f>
-      </c>
-    </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC57" s="3">
+        <f>IF($L57="","",U57-AB57)</f>
+      </c>
+    </row>
+    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="D58" s="2"/>
       <c r="K58" s="3"/>
@@ -3067,16 +3091,16 @@
         <f>IF($L58="","",M58-N58-O58-P58-Q58-R58-S58-T58)</f>
       </c>
       <c r="V58" s="3">
-        <f>IF($L58="","",(U58-X58)/K58*100)</f>
+        <f>IF($L58="","",(U58-AB58)/K58*100)</f>
       </c>
       <c r="W58" s="3">
         <f>IF($L58="","",N58-S58)</f>
       </c>
-      <c r="Y58" s="3">
-        <f>IF($L58="","",U58-X58)</f>
-      </c>
-    </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC58" s="3">
+        <f>IF($L58="","",U58-AB58)</f>
+      </c>
+    </row>
+    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="D59" s="2"/>
       <c r="K59" s="3"/>
@@ -3107,16 +3131,16 @@
         <f>IF($L59="","",M59-N59-O59-P59-Q59-R59-S59-T59)</f>
       </c>
       <c r="V59" s="3">
-        <f>IF($L59="","",(U59-X59)/K59*100)</f>
+        <f>IF($L59="","",(U59-AB59)/K59*100)</f>
       </c>
       <c r="W59" s="3">
         <f>IF($L59="","",N59-S59)</f>
       </c>
-      <c r="Y59" s="3">
-        <f>IF($L59="","",U59-X59)</f>
-      </c>
-    </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC59" s="3">
+        <f>IF($L59="","",U59-AB59)</f>
+      </c>
+    </row>
+    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="D60" s="2"/>
       <c r="K60" s="3"/>
@@ -3147,16 +3171,16 @@
         <f>IF($L60="","",M60-N60-O60-P60-Q60-R60-S60-T60)</f>
       </c>
       <c r="V60" s="3">
-        <f>IF($L60="","",(U60-X60)/K60*100)</f>
+        <f>IF($L60="","",(U60-AB60)/K60*100)</f>
       </c>
       <c r="W60" s="3">
         <f>IF($L60="","",N60-S60)</f>
       </c>
-      <c r="Y60" s="3">
-        <f>IF($L60="","",U60-X60)</f>
-      </c>
-    </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC60" s="3">
+        <f>IF($L60="","",U60-AB60)</f>
+      </c>
+    </row>
+    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="D61" s="2"/>
       <c r="K61" s="3"/>
@@ -3187,16 +3211,16 @@
         <f>IF($L61="","",M61-N61-O61-P61-Q61-R61-S61-T61)</f>
       </c>
       <c r="V61" s="3">
-        <f>IF($L61="","",(U61-X61)/K61*100)</f>
+        <f>IF($L61="","",(U61-AB61)/K61*100)</f>
       </c>
       <c r="W61" s="3">
         <f>IF($L61="","",N61-S61)</f>
       </c>
-      <c r="Y61" s="3">
-        <f>IF($L61="","",U61-X61)</f>
-      </c>
-    </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC61" s="3">
+        <f>IF($L61="","",U61-AB61)</f>
+      </c>
+    </row>
+    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="D62" s="2"/>
       <c r="K62" s="3"/>
@@ -3227,16 +3251,16 @@
         <f>IF($L62="","",M62-N62-O62-P62-Q62-R62-S62-T62)</f>
       </c>
       <c r="V62" s="3">
-        <f>IF($L62="","",(U62-X62)/K62*100)</f>
+        <f>IF($L62="","",(U62-AB62)/K62*100)</f>
       </c>
       <c r="W62" s="3">
         <f>IF($L62="","",N62-S62)</f>
       </c>
-      <c r="Y62" s="3">
-        <f>IF($L62="","",U62-X62)</f>
-      </c>
-    </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC62" s="3">
+        <f>IF($L62="","",U62-AB62)</f>
+      </c>
+    </row>
+    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="D63" s="2"/>
       <c r="K63" s="3"/>
@@ -3267,16 +3291,16 @@
         <f>IF($L63="","",M63-N63-O63-P63-Q63-R63-S63-T63)</f>
       </c>
       <c r="V63" s="3">
-        <f>IF($L63="","",(U63-X63)/K63*100)</f>
+        <f>IF($L63="","",(U63-AB63)/K63*100)</f>
       </c>
       <c r="W63" s="3">
         <f>IF($L63="","",N63-S63)</f>
       </c>
-      <c r="Y63" s="3">
-        <f>IF($L63="","",U63-X63)</f>
-      </c>
-    </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC63" s="3">
+        <f>IF($L63="","",U63-AB63)</f>
+      </c>
+    </row>
+    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="D64" s="2"/>
       <c r="K64" s="3"/>
@@ -3307,16 +3331,16 @@
         <f>IF($L64="","",M64-N64-O64-P64-Q64-R64-S64-T64)</f>
       </c>
       <c r="V64" s="3">
-        <f>IF($L64="","",(U64-X64)/K64*100)</f>
+        <f>IF($L64="","",(U64-AB64)/K64*100)</f>
       </c>
       <c r="W64" s="3">
         <f>IF($L64="","",N64-S64)</f>
       </c>
-      <c r="Y64" s="3">
-        <f>IF($L64="","",U64-X64)</f>
-      </c>
-    </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC64" s="3">
+        <f>IF($L64="","",U64-AB64)</f>
+      </c>
+    </row>
+    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="D65" s="2"/>
       <c r="K65" s="3"/>
@@ -3347,16 +3371,16 @@
         <f>IF($L65="","",M65-N65-O65-P65-Q65-R65-S65-T65)</f>
       </c>
       <c r="V65" s="3">
-        <f>IF($L65="","",(U65-X65)/K65*100)</f>
+        <f>IF($L65="","",(U65-AB65)/K65*100)</f>
       </c>
       <c r="W65" s="3">
         <f>IF($L65="","",N65-S65)</f>
       </c>
-      <c r="Y65" s="3">
-        <f>IF($L65="","",U65-X65)</f>
-      </c>
-    </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC65" s="3">
+        <f>IF($L65="","",U65-AB65)</f>
+      </c>
+    </row>
+    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="D66" s="2"/>
       <c r="K66" s="3"/>
@@ -3387,16 +3411,16 @@
         <f>IF($L66="","",M66-N66-O66-P66-Q66-R66-S66-T66)</f>
       </c>
       <c r="V66" s="3">
-        <f>IF($L66="","",(U66-X66)/K66*100)</f>
+        <f>IF($L66="","",(U66-AB66)/K66*100)</f>
       </c>
       <c r="W66" s="3">
         <f>IF($L66="","",N66-S66)</f>
       </c>
-      <c r="Y66" s="3">
-        <f>IF($L66="","",U66-X66)</f>
-      </c>
-    </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC66" s="3">
+        <f>IF($L66="","",U66-AB66)</f>
+      </c>
+    </row>
+    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="D67" s="2"/>
       <c r="K67" s="3"/>
@@ -3427,16 +3451,16 @@
         <f>IF($L67="","",M67-N67-O67-P67-Q67-R67-S67-T67)</f>
       </c>
       <c r="V67" s="3">
-        <f>IF($L67="","",(U67-X67)/K67*100)</f>
+        <f>IF($L67="","",(U67-AB67)/K67*100)</f>
       </c>
       <c r="W67" s="3">
         <f>IF($L67="","",N67-S67)</f>
       </c>
-      <c r="Y67" s="3">
-        <f>IF($L67="","",U67-X67)</f>
-      </c>
-    </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC67" s="3">
+        <f>IF($L67="","",U67-AB67)</f>
+      </c>
+    </row>
+    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="D68" s="2"/>
       <c r="K68" s="3"/>
@@ -3467,16 +3491,16 @@
         <f>IF($L68="","",M68-N68-O68-P68-Q68-R68-S68-T68)</f>
       </c>
       <c r="V68" s="3">
-        <f>IF($L68="","",(U68-X68)/K68*100)</f>
+        <f>IF($L68="","",(U68-AB68)/K68*100)</f>
       </c>
       <c r="W68" s="3">
         <f>IF($L68="","",N68-S68)</f>
       </c>
-      <c r="Y68" s="3">
-        <f>IF($L68="","",U68-X68)</f>
-      </c>
-    </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC68" s="3">
+        <f>IF($L68="","",U68-AB68)</f>
+      </c>
+    </row>
+    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="D69" s="2"/>
       <c r="K69" s="3"/>
@@ -3507,16 +3531,16 @@
         <f>IF($L69="","",M69-N69-O69-P69-Q69-R69-S69-T69)</f>
       </c>
       <c r="V69" s="3">
-        <f>IF($L69="","",(U69-X69)/K69*100)</f>
+        <f>IF($L69="","",(U69-AB69)/K69*100)</f>
       </c>
       <c r="W69" s="3">
         <f>IF($L69="","",N69-S69)</f>
       </c>
-      <c r="Y69" s="3">
-        <f>IF($L69="","",U69-X69)</f>
-      </c>
-    </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC69" s="3">
+        <f>IF($L69="","",U69-AB69)</f>
+      </c>
+    </row>
+    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="D70" s="2"/>
       <c r="K70" s="3"/>
@@ -3547,16 +3571,16 @@
         <f>IF($L70="","",M70-N70-O70-P70-Q70-R70-S70-T70)</f>
       </c>
       <c r="V70" s="3">
-        <f>IF($L70="","",(U70-X70)/K70*100)</f>
+        <f>IF($L70="","",(U70-AB70)/K70*100)</f>
       </c>
       <c r="W70" s="3">
         <f>IF($L70="","",N70-S70)</f>
       </c>
-      <c r="Y70" s="3">
-        <f>IF($L70="","",U70-X70)</f>
-      </c>
-    </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC70" s="3">
+        <f>IF($L70="","",U70-AB70)</f>
+      </c>
+    </row>
+    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="D71" s="2"/>
       <c r="K71" s="3"/>
@@ -3587,16 +3611,16 @@
         <f>IF($L71="","",M71-N71-O71-P71-Q71-R71-S71-T71)</f>
       </c>
       <c r="V71" s="3">
-        <f>IF($L71="","",(U71-X71)/K71*100)</f>
+        <f>IF($L71="","",(U71-AB71)/K71*100)</f>
       </c>
       <c r="W71" s="3">
         <f>IF($L71="","",N71-S71)</f>
       </c>
-      <c r="Y71" s="3">
-        <f>IF($L71="","",U71-X71)</f>
-      </c>
-    </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC71" s="3">
+        <f>IF($L71="","",U71-AB71)</f>
+      </c>
+    </row>
+    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="D72" s="2"/>
       <c r="K72" s="3"/>
@@ -3627,16 +3651,16 @@
         <f>IF($L72="","",M72-N72-O72-P72-Q72-R72-S72-T72)</f>
       </c>
       <c r="V72" s="3">
-        <f>IF($L72="","",(U72-X72)/K72*100)</f>
+        <f>IF($L72="","",(U72-AB72)/K72*100)</f>
       </c>
       <c r="W72" s="3">
         <f>IF($L72="","",N72-S72)</f>
       </c>
-      <c r="Y72" s="3">
-        <f>IF($L72="","",U72-X72)</f>
-      </c>
-    </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC72" s="3">
+        <f>IF($L72="","",U72-AB72)</f>
+      </c>
+    </row>
+    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="D73" s="2"/>
       <c r="K73" s="3"/>
@@ -3667,16 +3691,16 @@
         <f>IF($L73="","",M73-N73-O73-P73-Q73-R73-S73-T73)</f>
       </c>
       <c r="V73" s="3">
-        <f>IF($L73="","",(U73-X73)/K73*100)</f>
+        <f>IF($L73="","",(U73-AB73)/K73*100)</f>
       </c>
       <c r="W73" s="3">
         <f>IF($L73="","",N73-S73)</f>
       </c>
-      <c r="Y73" s="3">
-        <f>IF($L73="","",U73-X73)</f>
-      </c>
-    </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC73" s="3">
+        <f>IF($L73="","",U73-AB73)</f>
+      </c>
+    </row>
+    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="D74" s="2"/>
       <c r="K74" s="3"/>
@@ -3707,16 +3731,16 @@
         <f>IF($L74="","",M74-N74-O74-P74-Q74-R74-S74-T74)</f>
       </c>
       <c r="V74" s="3">
-        <f>IF($L74="","",(U74-X74)/K74*100)</f>
+        <f>IF($L74="","",(U74-AB74)/K74*100)</f>
       </c>
       <c r="W74" s="3">
         <f>IF($L74="","",N74-S74)</f>
       </c>
-      <c r="Y74" s="3">
-        <f>IF($L74="","",U74-X74)</f>
-      </c>
-    </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC74" s="3">
+        <f>IF($L74="","",U74-AB74)</f>
+      </c>
+    </row>
+    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="D75" s="2"/>
       <c r="K75" s="3"/>
@@ -3747,16 +3771,16 @@
         <f>IF($L75="","",M75-N75-O75-P75-Q75-R75-S75-T75)</f>
       </c>
       <c r="V75" s="3">
-        <f>IF($L75="","",(U75-X75)/K75*100)</f>
+        <f>IF($L75="","",(U75-AB75)/K75*100)</f>
       </c>
       <c r="W75" s="3">
         <f>IF($L75="","",N75-S75)</f>
       </c>
-      <c r="Y75" s="3">
-        <f>IF($L75="","",U75-X75)</f>
-      </c>
-    </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC75" s="3">
+        <f>IF($L75="","",U75-AB75)</f>
+      </c>
+    </row>
+    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="D76" s="2"/>
       <c r="K76" s="3"/>
@@ -3787,16 +3811,16 @@
         <f>IF($L76="","",M76-N76-O76-P76-Q76-R76-S76-T76)</f>
       </c>
       <c r="V76" s="3">
-        <f>IF($L76="","",(U76-X76)/K76*100)</f>
+        <f>IF($L76="","",(U76-AB76)/K76*100)</f>
       </c>
       <c r="W76" s="3">
         <f>IF($L76="","",N76-S76)</f>
       </c>
-      <c r="Y76" s="3">
-        <f>IF($L76="","",U76-X76)</f>
-      </c>
-    </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC76" s="3">
+        <f>IF($L76="","",U76-AB76)</f>
+      </c>
+    </row>
+    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="D77" s="2"/>
       <c r="K77" s="3"/>
@@ -3827,16 +3851,16 @@
         <f>IF($L77="","",M77-N77-O77-P77-Q77-R77-S77-T77)</f>
       </c>
       <c r="V77" s="3">
-        <f>IF($L77="","",(U77-X77)/K77*100)</f>
+        <f>IF($L77="","",(U77-AB77)/K77*100)</f>
       </c>
       <c r="W77" s="3">
         <f>IF($L77="","",N77-S77)</f>
       </c>
-      <c r="Y77" s="3">
-        <f>IF($L77="","",U77-X77)</f>
-      </c>
-    </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC77" s="3">
+        <f>IF($L77="","",U77-AB77)</f>
+      </c>
+    </row>
+    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="D78" s="2"/>
       <c r="K78" s="3"/>
@@ -3867,16 +3891,16 @@
         <f>IF($L78="","",M78-N78-O78-P78-Q78-R78-S78-T78)</f>
       </c>
       <c r="V78" s="3">
-        <f>IF($L78="","",(U78-X78)/K78*100)</f>
+        <f>IF($L78="","",(U78-AB78)/K78*100)</f>
       </c>
       <c r="W78" s="3">
         <f>IF($L78="","",N78-S78)</f>
       </c>
-      <c r="Y78" s="3">
-        <f>IF($L78="","",U78-X78)</f>
-      </c>
-    </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC78" s="3">
+        <f>IF($L78="","",U78-AB78)</f>
+      </c>
+    </row>
+    <row r="79" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="D79" s="2"/>
       <c r="K79" s="3"/>
@@ -3907,16 +3931,16 @@
         <f>IF($L79="","",M79-N79-O79-P79-Q79-R79-S79-T79)</f>
       </c>
       <c r="V79" s="3">
-        <f>IF($L79="","",(U79-X79)/K79*100)</f>
+        <f>IF($L79="","",(U79-AB79)/K79*100)</f>
       </c>
       <c r="W79" s="3">
         <f>IF($L79="","",N79-S79)</f>
       </c>
-      <c r="Y79" s="3">
-        <f>IF($L79="","",U79-X79)</f>
-      </c>
-    </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC79" s="3">
+        <f>IF($L79="","",U79-AB79)</f>
+      </c>
+    </row>
+    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="D80" s="2"/>
       <c r="K80" s="3"/>
@@ -3947,16 +3971,16 @@
         <f>IF($L80="","",M80-N80-O80-P80-Q80-R80-S80-T80)</f>
       </c>
       <c r="V80" s="3">
-        <f>IF($L80="","",(U80-X80)/K80*100)</f>
+        <f>IF($L80="","",(U80-AB80)/K80*100)</f>
       </c>
       <c r="W80" s="3">
         <f>IF($L80="","",N80-S80)</f>
       </c>
-      <c r="Y80" s="3">
-        <f>IF($L80="","",U80-X80)</f>
-      </c>
-    </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC80" s="3">
+        <f>IF($L80="","",U80-AB80)</f>
+      </c>
+    </row>
+    <row r="81" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="D81" s="2"/>
       <c r="K81" s="3"/>
@@ -3987,16 +4011,16 @@
         <f>IF($L81="","",M81-N81-O81-P81-Q81-R81-S81-T81)</f>
       </c>
       <c r="V81" s="3">
-        <f>IF($L81="","",(U81-X81)/K81*100)</f>
+        <f>IF($L81="","",(U81-AB81)/K81*100)</f>
       </c>
       <c r="W81" s="3">
         <f>IF($L81="","",N81-S81)</f>
       </c>
-      <c r="Y81" s="3">
-        <f>IF($L81="","",U81-X81)</f>
-      </c>
-    </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC81" s="3">
+        <f>IF($L81="","",U81-AB81)</f>
+      </c>
+    </row>
+    <row r="82" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="D82" s="2"/>
       <c r="K82" s="3"/>
@@ -4027,16 +4051,16 @@
         <f>IF($L82="","",M82-N82-O82-P82-Q82-R82-S82-T82)</f>
       </c>
       <c r="V82" s="3">
-        <f>IF($L82="","",(U82-X82)/K82*100)</f>
+        <f>IF($L82="","",(U82-AB82)/K82*100)</f>
       </c>
       <c r="W82" s="3">
         <f>IF($L82="","",N82-S82)</f>
       </c>
-      <c r="Y82" s="3">
-        <f>IF($L82="","",U82-X82)</f>
-      </c>
-    </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC82" s="3">
+        <f>IF($L82="","",U82-AB82)</f>
+      </c>
+    </row>
+    <row r="83" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="D83" s="2"/>
       <c r="K83" s="3"/>
@@ -4067,16 +4091,16 @@
         <f>IF($L83="","",M83-N83-O83-P83-Q83-R83-S83-T83)</f>
       </c>
       <c r="V83" s="3">
-        <f>IF($L83="","",(U83-X83)/K83*100)</f>
+        <f>IF($L83="","",(U83-AB83)/K83*100)</f>
       </c>
       <c r="W83" s="3">
         <f>IF($L83="","",N83-S83)</f>
       </c>
-      <c r="Y83" s="3">
-        <f>IF($L83="","",U83-X83)</f>
-      </c>
-    </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC83" s="3">
+        <f>IF($L83="","",U83-AB83)</f>
+      </c>
+    </row>
+    <row r="84" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="D84" s="2"/>
       <c r="K84" s="3"/>
@@ -4107,16 +4131,16 @@
         <f>IF($L84="","",M84-N84-O84-P84-Q84-R84-S84-T84)</f>
       </c>
       <c r="V84" s="3">
-        <f>IF($L84="","",(U84-X84)/K84*100)</f>
+        <f>IF($L84="","",(U84-AB84)/K84*100)</f>
       </c>
       <c r="W84" s="3">
         <f>IF($L84="","",N84-S84)</f>
       </c>
-      <c r="Y84" s="3">
-        <f>IF($L84="","",U84-X84)</f>
-      </c>
-    </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC84" s="3">
+        <f>IF($L84="","",U84-AB84)</f>
+      </c>
+    </row>
+    <row r="85" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="D85" s="2"/>
       <c r="K85" s="3"/>
@@ -4147,16 +4171,16 @@
         <f>IF($L85="","",M85-N85-O85-P85-Q85-R85-S85-T85)</f>
       </c>
       <c r="V85" s="3">
-        <f>IF($L85="","",(U85-X85)/K85*100)</f>
+        <f>IF($L85="","",(U85-AB85)/K85*100)</f>
       </c>
       <c r="W85" s="3">
         <f>IF($L85="","",N85-S85)</f>
       </c>
-      <c r="Y85" s="3">
-        <f>IF($L85="","",U85-X85)</f>
-      </c>
-    </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC85" s="3">
+        <f>IF($L85="","",U85-AB85)</f>
+      </c>
+    </row>
+    <row r="86" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="D86" s="2"/>
       <c r="K86" s="3"/>
@@ -4187,16 +4211,16 @@
         <f>IF($L86="","",M86-N86-O86-P86-Q86-R86-S86-T86)</f>
       </c>
       <c r="V86" s="3">
-        <f>IF($L86="","",(U86-X86)/K86*100)</f>
+        <f>IF($L86="","",(U86-AB86)/K86*100)</f>
       </c>
       <c r="W86" s="3">
         <f>IF($L86="","",N86-S86)</f>
       </c>
-      <c r="Y86" s="3">
-        <f>IF($L86="","",U86-X86)</f>
-      </c>
-    </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC86" s="3">
+        <f>IF($L86="","",U86-AB86)</f>
+      </c>
+    </row>
+    <row r="87" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="D87" s="2"/>
       <c r="K87" s="3"/>
@@ -4227,16 +4251,16 @@
         <f>IF($L87="","",M87-N87-O87-P87-Q87-R87-S87-T87)</f>
       </c>
       <c r="V87" s="3">
-        <f>IF($L87="","",(U87-X87)/K87*100)</f>
+        <f>IF($L87="","",(U87-AB87)/K87*100)</f>
       </c>
       <c r="W87" s="3">
         <f>IF($L87="","",N87-S87)</f>
       </c>
-      <c r="Y87" s="3">
-        <f>IF($L87="","",U87-X87)</f>
-      </c>
-    </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC87" s="3">
+        <f>IF($L87="","",U87-AB87)</f>
+      </c>
+    </row>
+    <row r="88" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="D88" s="2"/>
       <c r="K88" s="3"/>
@@ -4267,16 +4291,16 @@
         <f>IF($L88="","",M88-N88-O88-P88-Q88-R88-S88-T88)</f>
       </c>
       <c r="V88" s="3">
-        <f>IF($L88="","",(U88-X88)/K88*100)</f>
+        <f>IF($L88="","",(U88-AB88)/K88*100)</f>
       </c>
       <c r="W88" s="3">
         <f>IF($L88="","",N88-S88)</f>
       </c>
-      <c r="Y88" s="3">
-        <f>IF($L88="","",U88-X88)</f>
-      </c>
-    </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC88" s="3">
+        <f>IF($L88="","",U88-AB88)</f>
+      </c>
+    </row>
+    <row r="89" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="D89" s="2"/>
       <c r="K89" s="3"/>
@@ -4307,16 +4331,16 @@
         <f>IF($L89="","",M89-N89-O89-P89-Q89-R89-S89-T89)</f>
       </c>
       <c r="V89" s="3">
-        <f>IF($L89="","",(U89-X89)/K89*100)</f>
+        <f>IF($L89="","",(U89-AB89)/K89*100)</f>
       </c>
       <c r="W89" s="3">
         <f>IF($L89="","",N89-S89)</f>
       </c>
-      <c r="Y89" s="3">
-        <f>IF($L89="","",U89-X89)</f>
-      </c>
-    </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC89" s="3">
+        <f>IF($L89="","",U89-AB89)</f>
+      </c>
+    </row>
+    <row r="90" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="D90" s="2"/>
       <c r="K90" s="3"/>
@@ -4347,16 +4371,16 @@
         <f>IF($L90="","",M90-N90-O90-P90-Q90-R90-S90-T90)</f>
       </c>
       <c r="V90" s="3">
-        <f>IF($L90="","",(U90-X90)/K90*100)</f>
+        <f>IF($L90="","",(U90-AB90)/K90*100)</f>
       </c>
       <c r="W90" s="3">
         <f>IF($L90="","",N90-S90)</f>
       </c>
-      <c r="Y90" s="3">
-        <f>IF($L90="","",U90-X90)</f>
-      </c>
-    </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC90" s="3">
+        <f>IF($L90="","",U90-AB90)</f>
+      </c>
+    </row>
+    <row r="91" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="D91" s="2"/>
       <c r="K91" s="3"/>
@@ -4387,16 +4411,16 @@
         <f>IF($L91="","",M91-N91-O91-P91-Q91-R91-S91-T91)</f>
       </c>
       <c r="V91" s="3">
-        <f>IF($L91="","",(U91-X91)/K91*100)</f>
+        <f>IF($L91="","",(U91-AB91)/K91*100)</f>
       </c>
       <c r="W91" s="3">
         <f>IF($L91="","",N91-S91)</f>
       </c>
-      <c r="Y91" s="3">
-        <f>IF($L91="","",U91-X91)</f>
-      </c>
-    </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC91" s="3">
+        <f>IF($L91="","",U91-AB91)</f>
+      </c>
+    </row>
+    <row r="92" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="D92" s="2"/>
       <c r="K92" s="3"/>
@@ -4427,16 +4451,16 @@
         <f>IF($L92="","",M92-N92-O92-P92-Q92-R92-S92-T92)</f>
       </c>
       <c r="V92" s="3">
-        <f>IF($L92="","",(U92-X92)/K92*100)</f>
+        <f>IF($L92="","",(U92-AB92)/K92*100)</f>
       </c>
       <c r="W92" s="3">
         <f>IF($L92="","",N92-S92)</f>
       </c>
-      <c r="Y92" s="3">
-        <f>IF($L92="","",U92-X92)</f>
-      </c>
-    </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC92" s="3">
+        <f>IF($L92="","",U92-AB92)</f>
+      </c>
+    </row>
+    <row r="93" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="D93" s="2"/>
       <c r="K93" s="3"/>
@@ -4467,16 +4491,16 @@
         <f>IF($L93="","",M93-N93-O93-P93-Q93-R93-S93-T93)</f>
       </c>
       <c r="V93" s="3">
-        <f>IF($L93="","",(U93-X93)/K93*100)</f>
+        <f>IF($L93="","",(U93-AB93)/K93*100)</f>
       </c>
       <c r="W93" s="3">
         <f>IF($L93="","",N93-S93)</f>
       </c>
-      <c r="Y93" s="3">
-        <f>IF($L93="","",U93-X93)</f>
-      </c>
-    </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC93" s="3">
+        <f>IF($L93="","",U93-AB93)</f>
+      </c>
+    </row>
+    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="D94" s="2"/>
       <c r="K94" s="3"/>
@@ -4507,16 +4531,16 @@
         <f>IF($L94="","",M94-N94-O94-P94-Q94-R94-S94-T94)</f>
       </c>
       <c r="V94" s="3">
-        <f>IF($L94="","",(U94-X94)/K94*100)</f>
+        <f>IF($L94="","",(U94-AB94)/K94*100)</f>
       </c>
       <c r="W94" s="3">
         <f>IF($L94="","",N94-S94)</f>
       </c>
-      <c r="Y94" s="3">
-        <f>IF($L94="","",U94-X94)</f>
-      </c>
-    </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC94" s="3">
+        <f>IF($L94="","",U94-AB94)</f>
+      </c>
+    </row>
+    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="D95" s="2"/>
       <c r="K95" s="3"/>
@@ -4547,16 +4571,16 @@
         <f>IF($L95="","",M95-N95-O95-P95-Q95-R95-S95-T95)</f>
       </c>
       <c r="V95" s="3">
-        <f>IF($L95="","",(U95-X95)/K95*100)</f>
+        <f>IF($L95="","",(U95-AB95)/K95*100)</f>
       </c>
       <c r="W95" s="3">
         <f>IF($L95="","",N95-S95)</f>
       </c>
-      <c r="Y95" s="3">
-        <f>IF($L95="","",U95-X95)</f>
-      </c>
-    </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC95" s="3">
+        <f>IF($L95="","",U95-AB95)</f>
+      </c>
+    </row>
+    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="D96" s="2"/>
       <c r="K96" s="3"/>
@@ -4587,16 +4611,16 @@
         <f>IF($L96="","",M96-N96-O96-P96-Q96-R96-S96-T96)</f>
       </c>
       <c r="V96" s="3">
-        <f>IF($L96="","",(U96-X96)/K96*100)</f>
+        <f>IF($L96="","",(U96-AB96)/K96*100)</f>
       </c>
       <c r="W96" s="3">
         <f>IF($L96="","",N96-S96)</f>
       </c>
-      <c r="Y96" s="3">
-        <f>IF($L96="","",U96-X96)</f>
-      </c>
-    </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC96" s="3">
+        <f>IF($L96="","",U96-AB96)</f>
+      </c>
+    </row>
+    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="2"/>
       <c r="K97" s="3"/>
@@ -4627,16 +4651,16 @@
         <f>IF($L97="","",M97-N97-O97-P97-Q97-R97-S97-T97)</f>
       </c>
       <c r="V97" s="3">
-        <f>IF($L97="","",(U97-X97)/K97*100)</f>
+        <f>IF($L97="","",(U97-AB97)/K97*100)</f>
       </c>
       <c r="W97" s="3">
         <f>IF($L97="","",N97-S97)</f>
       </c>
-      <c r="Y97" s="3">
-        <f>IF($L97="","",U97-X97)</f>
-      </c>
-    </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC97" s="3">
+        <f>IF($L97="","",U97-AB97)</f>
+      </c>
+    </row>
+    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="D98" s="2"/>
       <c r="K98" s="3"/>
@@ -4667,16 +4691,16 @@
         <f>IF($L98="","",M98-N98-O98-P98-Q98-R98-S98-T98)</f>
       </c>
       <c r="V98" s="3">
-        <f>IF($L98="","",(U98-X98)/K98*100)</f>
+        <f>IF($L98="","",(U98-AB98)/K98*100)</f>
       </c>
       <c r="W98" s="3">
         <f>IF($L98="","",N98-S98)</f>
       </c>
-      <c r="Y98" s="3">
-        <f>IF($L98="","",U98-X98)</f>
-      </c>
-    </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC98" s="3">
+        <f>IF($L98="","",U98-AB98)</f>
+      </c>
+    </row>
+    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="D99" s="2"/>
       <c r="K99" s="3"/>
@@ -4707,16 +4731,16 @@
         <f>IF($L99="","",M99-N99-O99-P99-Q99-R99-S99-T99)</f>
       </c>
       <c r="V99" s="3">
-        <f>IF($L99="","",(U99-X99)/K99*100)</f>
+        <f>IF($L99="","",(U99-AB99)/K99*100)</f>
       </c>
       <c r="W99" s="3">
         <f>IF($L99="","",N99-S99)</f>
       </c>
-      <c r="Y99" s="3">
-        <f>IF($L99="","",U99-X99)</f>
-      </c>
-    </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC99" s="3">
+        <f>IF($L99="","",U99-AB99)</f>
+      </c>
+    </row>
+    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="D100" s="2"/>
       <c r="K100" s="3"/>
@@ -4747,16 +4771,16 @@
         <f>IF($L100="","",M100-N100-O100-P100-Q100-R100-S100-T100)</f>
       </c>
       <c r="V100" s="3">
-        <f>IF($L100="","",(U100-X100)/K100*100)</f>
+        <f>IF($L100="","",(U100-AB100)/K100*100)</f>
       </c>
       <c r="W100" s="3">
         <f>IF($L100="","",N100-S100)</f>
       </c>
-      <c r="Y100" s="3">
-        <f>IF($L100="","",U100-X100)</f>
-      </c>
-    </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC100" s="3">
+        <f>IF($L100="","",U100-AB100)</f>
+      </c>
+    </row>
+    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="D101" s="2"/>
       <c r="K101" s="3"/>
@@ -4787,16 +4811,16 @@
         <f>IF($L101="","",M101-N101-O101-P101-Q101-R101-S101-T101)</f>
       </c>
       <c r="V101" s="3">
-        <f>IF($L101="","",(U101-X101)/K101*100)</f>
+        <f>IF($L101="","",(U101-AB101)/K101*100)</f>
       </c>
       <c r="W101" s="3">
         <f>IF($L101="","",N101-S101)</f>
       </c>
-      <c r="Y101" s="3">
-        <f>IF($L101="","",U101-X101)</f>
-      </c>
-    </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC101" s="3">
+        <f>IF($L101="","",U101-AB101)</f>
+      </c>
+    </row>
+    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="D102" s="2"/>
       <c r="K102" s="3"/>
@@ -4827,16 +4851,16 @@
         <f>IF($L102="","",M102-N102-O102-P102-Q102-R102-S102-T102)</f>
       </c>
       <c r="V102" s="3">
-        <f>IF($L102="","",(U102-X102)/K102*100)</f>
+        <f>IF($L102="","",(U102-AB102)/K102*100)</f>
       </c>
       <c r="W102" s="3">
         <f>IF($L102="","",N102-S102)</f>
       </c>
-      <c r="Y102" s="3">
-        <f>IF($L102="","",U102-X102)</f>
-      </c>
-    </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC102" s="3">
+        <f>IF($L102="","",U102-AB102)</f>
+      </c>
+    </row>
+    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="D103" s="2"/>
       <c r="K103" s="3"/>
@@ -4867,16 +4891,16 @@
         <f>IF($L103="","",M103-N103-O103-P103-Q103-R103-S103-T103)</f>
       </c>
       <c r="V103" s="3">
-        <f>IF($L103="","",(U103-X103)/K103*100)</f>
+        <f>IF($L103="","",(U103-AB103)/K103*100)</f>
       </c>
       <c r="W103" s="3">
         <f>IF($L103="","",N103-S103)</f>
       </c>
-      <c r="Y103" s="3">
-        <f>IF($L103="","",U103-X103)</f>
-      </c>
-    </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC103" s="3">
+        <f>IF($L103="","",U103-AB103)</f>
+      </c>
+    </row>
+    <row r="104" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="D104" s="2"/>
       <c r="K104" s="3"/>
@@ -4907,16 +4931,16 @@
         <f>IF($L104="","",M104-N104-O104-P104-Q104-R104-S104-T104)</f>
       </c>
       <c r="V104" s="3">
-        <f>IF($L104="","",(U104-X104)/K104*100)</f>
+        <f>IF($L104="","",(U104-AB104)/K104*100)</f>
       </c>
       <c r="W104" s="3">
         <f>IF($L104="","",N104-S104)</f>
       </c>
-      <c r="Y104" s="3">
-        <f>IF($L104="","",U104-X104)</f>
-      </c>
-    </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC104" s="3">
+        <f>IF($L104="","",U104-AB104)</f>
+      </c>
+    </row>
+    <row r="105" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="D105" s="2"/>
       <c r="K105" s="3"/>
@@ -4947,16 +4971,16 @@
         <f>IF($L105="","",M105-N105-O105-P105-Q105-R105-S105-T105)</f>
       </c>
       <c r="V105" s="3">
-        <f>IF($L105="","",(U105-X105)/K105*100)</f>
+        <f>IF($L105="","",(U105-AB105)/K105*100)</f>
       </c>
       <c r="W105" s="3">
         <f>IF($L105="","",N105-S105)</f>
       </c>
-      <c r="Y105" s="3">
-        <f>IF($L105="","",U105-X105)</f>
-      </c>
-    </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC105" s="3">
+        <f>IF($L105="","",U105-AB105)</f>
+      </c>
+    </row>
+    <row r="106" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="D106" s="2"/>
       <c r="K106" s="3"/>
@@ -4987,16 +5011,16 @@
         <f>IF($L106="","",M106-N106-O106-P106-Q106-R106-S106-T106)</f>
       </c>
       <c r="V106" s="3">
-        <f>IF($L106="","",(U106-X106)/K106*100)</f>
+        <f>IF($L106="","",(U106-AB106)/K106*100)</f>
       </c>
       <c r="W106" s="3">
         <f>IF($L106="","",N106-S106)</f>
       </c>
-      <c r="Y106" s="3">
-        <f>IF($L106="","",U106-X106)</f>
-      </c>
-    </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC106" s="3">
+        <f>IF($L106="","",U106-AB106)</f>
+      </c>
+    </row>
+    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="D107" s="2"/>
       <c r="K107" s="3"/>
@@ -5027,16 +5051,16 @@
         <f>IF($L107="","",M107-N107-O107-P107-Q107-R107-S107-T107)</f>
       </c>
       <c r="V107" s="3">
-        <f>IF($L107="","",(U107-X107)/K107*100)</f>
+        <f>IF($L107="","",(U107-AB107)/K107*100)</f>
       </c>
       <c r="W107" s="3">
         <f>IF($L107="","",N107-S107)</f>
       </c>
-      <c r="Y107" s="3">
-        <f>IF($L107="","",U107-X107)</f>
-      </c>
-    </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC107" s="3">
+        <f>IF($L107="","",U107-AB107)</f>
+      </c>
+    </row>
+    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="D108" s="2"/>
       <c r="K108" s="3"/>
@@ -5067,16 +5091,16 @@
         <f>IF($L108="","",M108-N108-O108-P108-Q108-R108-S108-T108)</f>
       </c>
       <c r="V108" s="3">
-        <f>IF($L108="","",(U108-X108)/K108*100)</f>
+        <f>IF($L108="","",(U108-AB108)/K108*100)</f>
       </c>
       <c r="W108" s="3">
         <f>IF($L108="","",N108-S108)</f>
       </c>
-      <c r="Y108" s="3">
-        <f>IF($L108="","",U108-X108)</f>
-      </c>
-    </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC108" s="3">
+        <f>IF($L108="","",U108-AB108)</f>
+      </c>
+    </row>
+    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="D109" s="2"/>
       <c r="K109" s="3"/>
@@ -5107,16 +5131,16 @@
         <f>IF($L109="","",M109-N109-O109-P109-Q109-R109-S109-T109)</f>
       </c>
       <c r="V109" s="3">
-        <f>IF($L109="","",(U109-X109)/K109*100)</f>
+        <f>IF($L109="","",(U109-AB109)/K109*100)</f>
       </c>
       <c r="W109" s="3">
         <f>IF($L109="","",N109-S109)</f>
       </c>
-      <c r="Y109" s="3">
-        <f>IF($L109="","",U109-X109)</f>
-      </c>
-    </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC109" s="3">
+        <f>IF($L109="","",U109-AB109)</f>
+      </c>
+    </row>
+    <row r="110" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="D110" s="2"/>
       <c r="K110" s="3"/>
@@ -5147,16 +5171,16 @@
         <f>IF($L110="","",M110-N110-O110-P110-Q110-R110-S110-T110)</f>
       </c>
       <c r="V110" s="3">
-        <f>IF($L110="","",(U110-X110)/K110*100)</f>
+        <f>IF($L110="","",(U110-AB110)/K110*100)</f>
       </c>
       <c r="W110" s="3">
         <f>IF($L110="","",N110-S110)</f>
       </c>
-      <c r="Y110" s="3">
-        <f>IF($L110="","",U110-X110)</f>
-      </c>
-    </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC110" s="3">
+        <f>IF($L110="","",U110-AB110)</f>
+      </c>
+    </row>
+    <row r="111" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="D111" s="2"/>
       <c r="K111" s="3"/>
@@ -5187,16 +5211,16 @@
         <f>IF($L111="","",M111-N111-O111-P111-Q111-R111-S111-T111)</f>
       </c>
       <c r="V111" s="3">
-        <f>IF($L111="","",(U111-X111)/K111*100)</f>
+        <f>IF($L111="","",(U111-AB111)/K111*100)</f>
       </c>
       <c r="W111" s="3">
         <f>IF($L111="","",N111-S111)</f>
       </c>
-      <c r="Y111" s="3">
-        <f>IF($L111="","",U111-X111)</f>
-      </c>
-    </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC111" s="3">
+        <f>IF($L111="","",U111-AB111)</f>
+      </c>
+    </row>
+    <row r="112" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="D112" s="2"/>
       <c r="K112" s="3"/>
@@ -5227,16 +5251,16 @@
         <f>IF($L112="","",M112-N112-O112-P112-Q112-R112-S112-T112)</f>
       </c>
       <c r="V112" s="3">
-        <f>IF($L112="","",(U112-X112)/K112*100)</f>
+        <f>IF($L112="","",(U112-AB112)/K112*100)</f>
       </c>
       <c r="W112" s="3">
         <f>IF($L112="","",N112-S112)</f>
       </c>
-      <c r="Y112" s="3">
-        <f>IF($L112="","",U112-X112)</f>
-      </c>
-    </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC112" s="3">
+        <f>IF($L112="","",U112-AB112)</f>
+      </c>
+    </row>
+    <row r="113" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="D113" s="2"/>
       <c r="K113" s="3"/>
@@ -5267,16 +5291,16 @@
         <f>IF($L113="","",M113-N113-O113-P113-Q113-R113-S113-T113)</f>
       </c>
       <c r="V113" s="3">
-        <f>IF($L113="","",(U113-X113)/K113*100)</f>
+        <f>IF($L113="","",(U113-AB113)/K113*100)</f>
       </c>
       <c r="W113" s="3">
         <f>IF($L113="","",N113-S113)</f>
       </c>
-      <c r="Y113" s="3">
-        <f>IF($L113="","",U113-X113)</f>
-      </c>
-    </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC113" s="3">
+        <f>IF($L113="","",U113-AB113)</f>
+      </c>
+    </row>
+    <row r="114" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="D114" s="2"/>
       <c r="K114" s="3"/>
@@ -5307,16 +5331,16 @@
         <f>IF($L114="","",M114-N114-O114-P114-Q114-R114-S114-T114)</f>
       </c>
       <c r="V114" s="3">
-        <f>IF($L114="","",(U114-X114)/K114*100)</f>
+        <f>IF($L114="","",(U114-AB114)/K114*100)</f>
       </c>
       <c r="W114" s="3">
         <f>IF($L114="","",N114-S114)</f>
       </c>
-      <c r="Y114" s="3">
-        <f>IF($L114="","",U114-X114)</f>
-      </c>
-    </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC114" s="3">
+        <f>IF($L114="","",U114-AB114)</f>
+      </c>
+    </row>
+    <row r="115" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="D115" s="2"/>
       <c r="K115" s="3"/>
@@ -5347,16 +5371,16 @@
         <f>IF($L115="","",M115-N115-O115-P115-Q115-R115-S115-T115)</f>
       </c>
       <c r="V115" s="3">
-        <f>IF($L115="","",(U115-X115)/K115*100)</f>
+        <f>IF($L115="","",(U115-AB115)/K115*100)</f>
       </c>
       <c r="W115" s="3">
         <f>IF($L115="","",N115-S115)</f>
       </c>
-      <c r="Y115" s="3">
-        <f>IF($L115="","",U115-X115)</f>
-      </c>
-    </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC115" s="3">
+        <f>IF($L115="","",U115-AB115)</f>
+      </c>
+    </row>
+    <row r="116" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="D116" s="2"/>
       <c r="K116" s="3"/>
@@ -5387,16 +5411,16 @@
         <f>IF($L116="","",M116-N116-O116-P116-Q116-R116-S116-T116)</f>
       </c>
       <c r="V116" s="3">
-        <f>IF($L116="","",(U116-X116)/K116*100)</f>
+        <f>IF($L116="","",(U116-AB116)/K116*100)</f>
       </c>
       <c r="W116" s="3">
         <f>IF($L116="","",N116-S116)</f>
       </c>
-      <c r="Y116" s="3">
-        <f>IF($L116="","",U116-X116)</f>
-      </c>
-    </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC116" s="3">
+        <f>IF($L116="","",U116-AB116)</f>
+      </c>
+    </row>
+    <row r="117" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="D117" s="2"/>
       <c r="K117" s="3"/>
@@ -5427,16 +5451,16 @@
         <f>IF($L117="","",M117-N117-O117-P117-Q117-R117-S117-T117)</f>
       </c>
       <c r="V117" s="3">
-        <f>IF($L117="","",(U117-X117)/K117*100)</f>
+        <f>IF($L117="","",(U117-AB117)/K117*100)</f>
       </c>
       <c r="W117" s="3">
         <f>IF($L117="","",N117-S117)</f>
       </c>
-      <c r="Y117" s="3">
-        <f>IF($L117="","",U117-X117)</f>
-      </c>
-    </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC117" s="3">
+        <f>IF($L117="","",U117-AB117)</f>
+      </c>
+    </row>
+    <row r="118" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="D118" s="2"/>
       <c r="K118" s="3"/>
@@ -5467,16 +5491,16 @@
         <f>IF($L118="","",M118-N118-O118-P118-Q118-R118-S118-T118)</f>
       </c>
       <c r="V118" s="3">
-        <f>IF($L118="","",(U118-X118)/K118*100)</f>
+        <f>IF($L118="","",(U118-AB118)/K118*100)</f>
       </c>
       <c r="W118" s="3">
         <f>IF($L118="","",N118-S118)</f>
       </c>
-      <c r="Y118" s="3">
-        <f>IF($L118="","",U118-X118)</f>
-      </c>
-    </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC118" s="3">
+        <f>IF($L118="","",U118-AB118)</f>
+      </c>
+    </row>
+    <row r="119" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="D119" s="2"/>
       <c r="K119" s="3"/>
@@ -5507,16 +5531,16 @@
         <f>IF($L119="","",M119-N119-O119-P119-Q119-R119-S119-T119)</f>
       </c>
       <c r="V119" s="3">
-        <f>IF($L119="","",(U119-X119)/K119*100)</f>
+        <f>IF($L119="","",(U119-AB119)/K119*100)</f>
       </c>
       <c r="W119" s="3">
         <f>IF($L119="","",N119-S119)</f>
       </c>
-      <c r="Y119" s="3">
-        <f>IF($L119="","",U119-X119)</f>
-      </c>
-    </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC119" s="3">
+        <f>IF($L119="","",U119-AB119)</f>
+      </c>
+    </row>
+    <row r="120" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="D120" s="2"/>
       <c r="K120" s="3"/>
@@ -5547,16 +5571,16 @@
         <f>IF($L120="","",M120-N120-O120-P120-Q120-R120-S120-T120)</f>
       </c>
       <c r="V120" s="3">
-        <f>IF($L120="","",(U120-X120)/K120*100)</f>
+        <f>IF($L120="","",(U120-AB120)/K120*100)</f>
       </c>
       <c r="W120" s="3">
         <f>IF($L120="","",N120-S120)</f>
       </c>
-      <c r="Y120" s="3">
-        <f>IF($L120="","",U120-X120)</f>
-      </c>
-    </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC120" s="3">
+        <f>IF($L120="","",U120-AB120)</f>
+      </c>
+    </row>
+    <row r="121" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="D121" s="2"/>
       <c r="K121" s="3"/>
@@ -5587,16 +5611,16 @@
         <f>IF($L121="","",M121-N121-O121-P121-Q121-R121-S121-T121)</f>
       </c>
       <c r="V121" s="3">
-        <f>IF($L121="","",(U121-X121)/K121*100)</f>
+        <f>IF($L121="","",(U121-AB121)/K121*100)</f>
       </c>
       <c r="W121" s="3">
         <f>IF($L121="","",N121-S121)</f>
       </c>
-      <c r="Y121" s="3">
-        <f>IF($L121="","",U121-X121)</f>
-      </c>
-    </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC121" s="3">
+        <f>IF($L121="","",U121-AB121)</f>
+      </c>
+    </row>
+    <row r="122" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="D122" s="2"/>
       <c r="K122" s="3"/>
@@ -5627,16 +5651,16 @@
         <f>IF($L122="","",M122-N122-O122-P122-Q122-R122-S122-T122)</f>
       </c>
       <c r="V122" s="3">
-        <f>IF($L122="","",(U122-X122)/K122*100)</f>
+        <f>IF($L122="","",(U122-AB122)/K122*100)</f>
       </c>
       <c r="W122" s="3">
         <f>IF($L122="","",N122-S122)</f>
       </c>
-      <c r="Y122" s="3">
-        <f>IF($L122="","",U122-X122)</f>
-      </c>
-    </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC122" s="3">
+        <f>IF($L122="","",U122-AB122)</f>
+      </c>
+    </row>
+    <row r="123" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="D123" s="2"/>
       <c r="K123" s="3"/>
@@ -5667,16 +5691,16 @@
         <f>IF($L123="","",M123-N123-O123-P123-Q123-R123-S123-T123)</f>
       </c>
       <c r="V123" s="3">
-        <f>IF($L123="","",(U123-X123)/K123*100)</f>
+        <f>IF($L123="","",(U123-AB123)/K123*100)</f>
       </c>
       <c r="W123" s="3">
         <f>IF($L123="","",N123-S123)</f>
       </c>
-      <c r="Y123" s="3">
-        <f>IF($L123="","",U123-X123)</f>
-      </c>
-    </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC123" s="3">
+        <f>IF($L123="","",U123-AB123)</f>
+      </c>
+    </row>
+    <row r="124" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="D124" s="2"/>
       <c r="K124" s="3"/>
@@ -5707,16 +5731,16 @@
         <f>IF($L124="","",M124-N124-O124-P124-Q124-R124-S124-T124)</f>
       </c>
       <c r="V124" s="3">
-        <f>IF($L124="","",(U124-X124)/K124*100)</f>
+        <f>IF($L124="","",(U124-AB124)/K124*100)</f>
       </c>
       <c r="W124" s="3">
         <f>IF($L124="","",N124-S124)</f>
       </c>
-      <c r="Y124" s="3">
-        <f>IF($L124="","",U124-X124)</f>
-      </c>
-    </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC124" s="3">
+        <f>IF($L124="","",U124-AB124)</f>
+      </c>
+    </row>
+    <row r="125" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="D125" s="2"/>
       <c r="K125" s="3"/>
@@ -5747,16 +5771,16 @@
         <f>IF($L125="","",M125-N125-O125-P125-Q125-R125-S125-T125)</f>
       </c>
       <c r="V125" s="3">
-        <f>IF($L125="","",(U125-X125)/K125*100)</f>
+        <f>IF($L125="","",(U125-AB125)/K125*100)</f>
       </c>
       <c r="W125" s="3">
         <f>IF($L125="","",N125-S125)</f>
       </c>
-      <c r="Y125" s="3">
-        <f>IF($L125="","",U125-X125)</f>
-      </c>
-    </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC125" s="3">
+        <f>IF($L125="","",U125-AB125)</f>
+      </c>
+    </row>
+    <row r="126" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="D126" s="2"/>
       <c r="K126" s="3"/>
@@ -5787,16 +5811,16 @@
         <f>IF($L126="","",M126-N126-O126-P126-Q126-R126-S126-T126)</f>
       </c>
       <c r="V126" s="3">
-        <f>IF($L126="","",(U126-X126)/K126*100)</f>
+        <f>IF($L126="","",(U126-AB126)/K126*100)</f>
       </c>
       <c r="W126" s="3">
         <f>IF($L126="","",N126-S126)</f>
       </c>
-      <c r="Y126" s="3">
-        <f>IF($L126="","",U126-X126)</f>
-      </c>
-    </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC126" s="3">
+        <f>IF($L126="","",U126-AB126)</f>
+      </c>
+    </row>
+    <row r="127" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="D127" s="2"/>
       <c r="K127" s="3"/>
@@ -5827,16 +5851,16 @@
         <f>IF($L127="","",M127-N127-O127-P127-Q127-R127-S127-T127)</f>
       </c>
       <c r="V127" s="3">
-        <f>IF($L127="","",(U127-X127)/K127*100)</f>
+        <f>IF($L127="","",(U127-AB127)/K127*100)</f>
       </c>
       <c r="W127" s="3">
         <f>IF($L127="","",N127-S127)</f>
       </c>
-      <c r="Y127" s="3">
-        <f>IF($L127="","",U127-X127)</f>
-      </c>
-    </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC127" s="3">
+        <f>IF($L127="","",U127-AB127)</f>
+      </c>
+    </row>
+    <row r="128" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="D128" s="2"/>
       <c r="K128" s="3"/>
@@ -5867,16 +5891,16 @@
         <f>IF($L128="","",M128-N128-O128-P128-Q128-R128-S128-T128)</f>
       </c>
       <c r="V128" s="3">
-        <f>IF($L128="","",(U128-X128)/K128*100)</f>
+        <f>IF($L128="","",(U128-AB128)/K128*100)</f>
       </c>
       <c r="W128" s="3">
         <f>IF($L128="","",N128-S128)</f>
       </c>
-      <c r="Y128" s="3">
-        <f>IF($L128="","",U128-X128)</f>
-      </c>
-    </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC128" s="3">
+        <f>IF($L128="","",U128-AB128)</f>
+      </c>
+    </row>
+    <row r="129" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="D129" s="2"/>
       <c r="K129" s="3"/>
@@ -5907,16 +5931,16 @@
         <f>IF($L129="","",M129-N129-O129-P129-Q129-R129-S129-T129)</f>
       </c>
       <c r="V129" s="3">
-        <f>IF($L129="","",(U129-X129)/K129*100)</f>
+        <f>IF($L129="","",(U129-AB129)/K129*100)</f>
       </c>
       <c r="W129" s="3">
         <f>IF($L129="","",N129-S129)</f>
       </c>
-      <c r="Y129" s="3">
-        <f>IF($L129="","",U129-X129)</f>
-      </c>
-    </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC129" s="3">
+        <f>IF($L129="","",U129-AB129)</f>
+      </c>
+    </row>
+    <row r="130" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="D130" s="2"/>
       <c r="K130" s="3"/>
@@ -5947,16 +5971,16 @@
         <f>IF($L130="","",M130-N130-O130-P130-Q130-R130-S130-T130)</f>
       </c>
       <c r="V130" s="3">
-        <f>IF($L130="","",(U130-X130)/K130*100)</f>
+        <f>IF($L130="","",(U130-AB130)/K130*100)</f>
       </c>
       <c r="W130" s="3">
         <f>IF($L130="","",N130-S130)</f>
       </c>
-      <c r="Y130" s="3">
-        <f>IF($L130="","",U130-X130)</f>
-      </c>
-    </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC130" s="3">
+        <f>IF($L130="","",U130-AB130)</f>
+      </c>
+    </row>
+    <row r="131" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="D131" s="2"/>
       <c r="K131" s="3"/>
@@ -5987,16 +6011,16 @@
         <f>IF($L131="","",M131-N131-O131-P131-Q131-R131-S131-T131)</f>
       </c>
       <c r="V131" s="3">
-        <f>IF($L131="","",(U131-X131)/K131*100)</f>
+        <f>IF($L131="","",(U131-AB131)/K131*100)</f>
       </c>
       <c r="W131" s="3">
         <f>IF($L131="","",N131-S131)</f>
       </c>
-      <c r="Y131" s="3">
-        <f>IF($L131="","",U131-X131)</f>
-      </c>
-    </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC131" s="3">
+        <f>IF($L131="","",U131-AB131)</f>
+      </c>
+    </row>
+    <row r="132" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="D132" s="2"/>
       <c r="K132" s="3"/>
@@ -6027,16 +6051,16 @@
         <f>IF($L132="","",M132-N132-O132-P132-Q132-R132-S132-T132)</f>
       </c>
       <c r="V132" s="3">
-        <f>IF($L132="","",(U132-X132)/K132*100)</f>
+        <f>IF($L132="","",(U132-AB132)/K132*100)</f>
       </c>
       <c r="W132" s="3">
         <f>IF($L132="","",N132-S132)</f>
       </c>
-      <c r="Y132" s="3">
-        <f>IF($L132="","",U132-X132)</f>
-      </c>
-    </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC132" s="3">
+        <f>IF($L132="","",U132-AB132)</f>
+      </c>
+    </row>
+    <row r="133" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="D133" s="2"/>
       <c r="K133" s="3"/>
@@ -6067,16 +6091,16 @@
         <f>IF($L133="","",M133-N133-O133-P133-Q133-R133-S133-T133)</f>
       </c>
       <c r="V133" s="3">
-        <f>IF($L133="","",(U133-X133)/K133*100)</f>
+        <f>IF($L133="","",(U133-AB133)/K133*100)</f>
       </c>
       <c r="W133" s="3">
         <f>IF($L133="","",N133-S133)</f>
       </c>
-      <c r="Y133" s="3">
-        <f>IF($L133="","",U133-X133)</f>
-      </c>
-    </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC133" s="3">
+        <f>IF($L133="","",U133-AB133)</f>
+      </c>
+    </row>
+    <row r="134" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="D134" s="2"/>
       <c r="K134" s="3"/>
@@ -6107,16 +6131,16 @@
         <f>IF($L134="","",M134-N134-O134-P134-Q134-R134-S134-T134)</f>
       </c>
       <c r="V134" s="3">
-        <f>IF($L134="","",(U134-X134)/K134*100)</f>
+        <f>IF($L134="","",(U134-AB134)/K134*100)</f>
       </c>
       <c r="W134" s="3">
         <f>IF($L134="","",N134-S134)</f>
       </c>
-      <c r="Y134" s="3">
-        <f>IF($L134="","",U134-X134)</f>
-      </c>
-    </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC134" s="3">
+        <f>IF($L134="","",U134-AB134)</f>
+      </c>
+    </row>
+    <row r="135" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="D135" s="2"/>
       <c r="K135" s="3"/>
@@ -6147,16 +6171,16 @@
         <f>IF($L135="","",M135-N135-O135-P135-Q135-R135-S135-T135)</f>
       </c>
       <c r="V135" s="3">
-        <f>IF($L135="","",(U135-X135)/K135*100)</f>
+        <f>IF($L135="","",(U135-AB135)/K135*100)</f>
       </c>
       <c r="W135" s="3">
         <f>IF($L135="","",N135-S135)</f>
       </c>
-      <c r="Y135" s="3">
-        <f>IF($L135="","",U135-X135)</f>
-      </c>
-    </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC135" s="3">
+        <f>IF($L135="","",U135-AB135)</f>
+      </c>
+    </row>
+    <row r="136" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="D136" s="2"/>
       <c r="K136" s="3"/>
@@ -6187,16 +6211,16 @@
         <f>IF($L136="","",M136-N136-O136-P136-Q136-R136-S136-T136)</f>
       </c>
       <c r="V136" s="3">
-        <f>IF($L136="","",(U136-X136)/K136*100)</f>
+        <f>IF($L136="","",(U136-AB136)/K136*100)</f>
       </c>
       <c r="W136" s="3">
         <f>IF($L136="","",N136-S136)</f>
       </c>
-      <c r="Y136" s="3">
-        <f>IF($L136="","",U136-X136)</f>
-      </c>
-    </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC136" s="3">
+        <f>IF($L136="","",U136-AB136)</f>
+      </c>
+    </row>
+    <row r="137" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="D137" s="2"/>
       <c r="K137" s="3"/>
@@ -6227,16 +6251,16 @@
         <f>IF($L137="","",M137-N137-O137-P137-Q137-R137-S137-T137)</f>
       </c>
       <c r="V137" s="3">
-        <f>IF($L137="","",(U137-X137)/K137*100)</f>
+        <f>IF($L137="","",(U137-AB137)/K137*100)</f>
       </c>
       <c r="W137" s="3">
         <f>IF($L137="","",N137-S137)</f>
       </c>
-      <c r="Y137" s="3">
-        <f>IF($L137="","",U137-X137)</f>
-      </c>
-    </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC137" s="3">
+        <f>IF($L137="","",U137-AB137)</f>
+      </c>
+    </row>
+    <row r="138" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="D138" s="2"/>
       <c r="K138" s="3"/>
@@ -6267,16 +6291,16 @@
         <f>IF($L138="","",M138-N138-O138-P138-Q138-R138-S138-T138)</f>
       </c>
       <c r="V138" s="3">
-        <f>IF($L138="","",(U138-X138)/K138*100)</f>
+        <f>IF($L138="","",(U138-AB138)/K138*100)</f>
       </c>
       <c r="W138" s="3">
         <f>IF($L138="","",N138-S138)</f>
       </c>
-      <c r="Y138" s="3">
-        <f>IF($L138="","",U138-X138)</f>
-      </c>
-    </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC138" s="3">
+        <f>IF($L138="","",U138-AB138)</f>
+      </c>
+    </row>
+    <row r="139" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="D139" s="2"/>
       <c r="K139" s="3"/>
@@ -6307,16 +6331,16 @@
         <f>IF($L139="","",M139-N139-O139-P139-Q139-R139-S139-T139)</f>
       </c>
       <c r="V139" s="3">
-        <f>IF($L139="","",(U139-X139)/K139*100)</f>
+        <f>IF($L139="","",(U139-AB139)/K139*100)</f>
       </c>
       <c r="W139" s="3">
         <f>IF($L139="","",N139-S139)</f>
       </c>
-      <c r="Y139" s="3">
-        <f>IF($L139="","",U139-X139)</f>
-      </c>
-    </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC139" s="3">
+        <f>IF($L139="","",U139-AB139)</f>
+      </c>
+    </row>
+    <row r="140" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="D140" s="2"/>
       <c r="K140" s="3"/>
@@ -6347,16 +6371,16 @@
         <f>IF($L140="","",M140-N140-O140-P140-Q140-R140-S140-T140)</f>
       </c>
       <c r="V140" s="3">
-        <f>IF($L140="","",(U140-X140)/K140*100)</f>
+        <f>IF($L140="","",(U140-AB140)/K140*100)</f>
       </c>
       <c r="W140" s="3">
         <f>IF($L140="","",N140-S140)</f>
       </c>
-      <c r="Y140" s="3">
-        <f>IF($L140="","",U140-X140)</f>
-      </c>
-    </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC140" s="3">
+        <f>IF($L140="","",U140-AB140)</f>
+      </c>
+    </row>
+    <row r="141" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="D141" s="2"/>
       <c r="K141" s="3"/>
@@ -6387,16 +6411,16 @@
         <f>IF($L141="","",M141-N141-O141-P141-Q141-R141-S141-T141)</f>
       </c>
       <c r="V141" s="3">
-        <f>IF($L141="","",(U141-X141)/K141*100)</f>
+        <f>IF($L141="","",(U141-AB141)/K141*100)</f>
       </c>
       <c r="W141" s="3">
         <f>IF($L141="","",N141-S141)</f>
       </c>
-      <c r="Y141" s="3">
-        <f>IF($L141="","",U141-X141)</f>
-      </c>
-    </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC141" s="3">
+        <f>IF($L141="","",U141-AB141)</f>
+      </c>
+    </row>
+    <row r="142" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="D142" s="2"/>
       <c r="K142" s="3"/>
@@ -6427,16 +6451,16 @@
         <f>IF($L142="","",M142-N142-O142-P142-Q142-R142-S142-T142)</f>
       </c>
       <c r="V142" s="3">
-        <f>IF($L142="","",(U142-X142)/K142*100)</f>
+        <f>IF($L142="","",(U142-AB142)/K142*100)</f>
       </c>
       <c r="W142" s="3">
         <f>IF($L142="","",N142-S142)</f>
       </c>
-      <c r="Y142" s="3">
-        <f>IF($L142="","",U142-X142)</f>
-      </c>
-    </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC142" s="3">
+        <f>IF($L142="","",U142-AB142)</f>
+      </c>
+    </row>
+    <row r="143" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="D143" s="2"/>
       <c r="K143" s="3"/>
@@ -6467,16 +6491,16 @@
         <f>IF($L143="","",M143-N143-O143-P143-Q143-R143-S143-T143)</f>
       </c>
       <c r="V143" s="3">
-        <f>IF($L143="","",(U143-X143)/K143*100)</f>
+        <f>IF($L143="","",(U143-AB143)/K143*100)</f>
       </c>
       <c r="W143" s="3">
         <f>IF($L143="","",N143-S143)</f>
       </c>
-      <c r="Y143" s="3">
-        <f>IF($L143="","",U143-X143)</f>
-      </c>
-    </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC143" s="3">
+        <f>IF($L143="","",U143-AB143)</f>
+      </c>
+    </row>
+    <row r="144" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="D144" s="2"/>
       <c r="K144" s="3"/>
@@ -6507,16 +6531,16 @@
         <f>IF($L144="","",M144-N144-O144-P144-Q144-R144-S144-T144)</f>
       </c>
       <c r="V144" s="3">
-        <f>IF($L144="","",(U144-X144)/K144*100)</f>
+        <f>IF($L144="","",(U144-AB144)/K144*100)</f>
       </c>
       <c r="W144" s="3">
         <f>IF($L144="","",N144-S144)</f>
       </c>
-      <c r="Y144" s="3">
-        <f>IF($L144="","",U144-X144)</f>
-      </c>
-    </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC144" s="3">
+        <f>IF($L144="","",U144-AB144)</f>
+      </c>
+    </row>
+    <row r="145" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="D145" s="2"/>
       <c r="K145" s="3"/>
@@ -6547,16 +6571,16 @@
         <f>IF($L145="","",M145-N145-O145-P145-Q145-R145-S145-T145)</f>
       </c>
       <c r="V145" s="3">
-        <f>IF($L145="","",(U145-X145)/K145*100)</f>
+        <f>IF($L145="","",(U145-AB145)/K145*100)</f>
       </c>
       <c r="W145" s="3">
         <f>IF($L145="","",N145-S145)</f>
       </c>
-      <c r="Y145" s="3">
-        <f>IF($L145="","",U145-X145)</f>
-      </c>
-    </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC145" s="3">
+        <f>IF($L145="","",U145-AB145)</f>
+      </c>
+    </row>
+    <row r="146" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="D146" s="2"/>
       <c r="K146" s="3"/>
@@ -6587,16 +6611,16 @@
         <f>IF($L146="","",M146-N146-O146-P146-Q146-R146-S146-T146)</f>
       </c>
       <c r="V146" s="3">
-        <f>IF($L146="","",(U146-X146)/K146*100)</f>
+        <f>IF($L146="","",(U146-AB146)/K146*100)</f>
       </c>
       <c r="W146" s="3">
         <f>IF($L146="","",N146-S146)</f>
       </c>
-      <c r="Y146" s="3">
-        <f>IF($L146="","",U146-X146)</f>
-      </c>
-    </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC146" s="3">
+        <f>IF($L146="","",U146-AB146)</f>
+      </c>
+    </row>
+    <row r="147" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="D147" s="2"/>
       <c r="K147" s="3"/>
@@ -6627,16 +6651,16 @@
         <f>IF($L147="","",M147-N147-O147-P147-Q147-R147-S147-T147)</f>
       </c>
       <c r="V147" s="3">
-        <f>IF($L147="","",(U147-X147)/K147*100)</f>
+        <f>IF($L147="","",(U147-AB147)/K147*100)</f>
       </c>
       <c r="W147" s="3">
         <f>IF($L147="","",N147-S147)</f>
       </c>
-      <c r="Y147" s="3">
-        <f>IF($L147="","",U147-X147)</f>
-      </c>
-    </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC147" s="3">
+        <f>IF($L147="","",U147-AB147)</f>
+      </c>
+    </row>
+    <row r="148" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="D148" s="2"/>
       <c r="K148" s="3"/>
@@ -6667,16 +6691,16 @@
         <f>IF($L148="","",M148-N148-O148-P148-Q148-R148-S148-T148)</f>
       </c>
       <c r="V148" s="3">
-        <f>IF($L148="","",(U148-X148)/K148*100)</f>
+        <f>IF($L148="","",(U148-AB148)/K148*100)</f>
       </c>
       <c r="W148" s="3">
         <f>IF($L148="","",N148-S148)</f>
       </c>
-      <c r="Y148" s="3">
-        <f>IF($L148="","",U148-X148)</f>
-      </c>
-    </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC148" s="3">
+        <f>IF($L148="","",U148-AB148)</f>
+      </c>
+    </row>
+    <row r="149" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="D149" s="2"/>
       <c r="K149" s="3"/>
@@ -6707,16 +6731,16 @@
         <f>IF($L149="","",M149-N149-O149-P149-Q149-R149-S149-T149)</f>
       </c>
       <c r="V149" s="3">
-        <f>IF($L149="","",(U149-X149)/K149*100)</f>
+        <f>IF($L149="","",(U149-AB149)/K149*100)</f>
       </c>
       <c r="W149" s="3">
         <f>IF($L149="","",N149-S149)</f>
       </c>
-      <c r="Y149" s="3">
-        <f>IF($L149="","",U149-X149)</f>
-      </c>
-    </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC149" s="3">
+        <f>IF($L149="","",U149-AB149)</f>
+      </c>
+    </row>
+    <row r="150" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="D150" s="2"/>
       <c r="K150" s="3"/>
@@ -6747,16 +6771,16 @@
         <f>IF($L150="","",M150-N150-O150-P150-Q150-R150-S150-T150)</f>
       </c>
       <c r="V150" s="3">
-        <f>IF($L150="","",(U150-X150)/K150*100)</f>
+        <f>IF($L150="","",(U150-AB150)/K150*100)</f>
       </c>
       <c r="W150" s="3">
         <f>IF($L150="","",N150-S150)</f>
       </c>
-      <c r="Y150" s="3">
-        <f>IF($L150="","",U150-X150)</f>
-      </c>
-    </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC150" s="3">
+        <f>IF($L150="","",U150-AB150)</f>
+      </c>
+    </row>
+    <row r="151" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="D151" s="2"/>
       <c r="K151" s="3"/>
@@ -6787,16 +6811,16 @@
         <f>IF($L151="","",M151-N151-O151-P151-Q151-R151-S151-T151)</f>
       </c>
       <c r="V151" s="3">
-        <f>IF($L151="","",(U151-X151)/K151*100)</f>
+        <f>IF($L151="","",(U151-AB151)/K151*100)</f>
       </c>
       <c r="W151" s="3">
         <f>IF($L151="","",N151-S151)</f>
       </c>
-      <c r="Y151" s="3">
-        <f>IF($L151="","",U151-X151)</f>
-      </c>
-    </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC151" s="3">
+        <f>IF($L151="","",U151-AB151)</f>
+      </c>
+    </row>
+    <row r="152" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="D152" s="2"/>
       <c r="K152" s="3"/>
@@ -6827,16 +6851,16 @@
         <f>IF($L152="","",M152-N152-O152-P152-Q152-R152-S152-T152)</f>
       </c>
       <c r="V152" s="3">
-        <f>IF($L152="","",(U152-X152)/K152*100)</f>
+        <f>IF($L152="","",(U152-AB152)/K152*100)</f>
       </c>
       <c r="W152" s="3">
         <f>IF($L152="","",N152-S152)</f>
       </c>
-      <c r="Y152" s="3">
-        <f>IF($L152="","",U152-X152)</f>
-      </c>
-    </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC152" s="3">
+        <f>IF($L152="","",U152-AB152)</f>
+      </c>
+    </row>
+    <row r="153" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="D153" s="2"/>
       <c r="K153" s="3"/>
@@ -6867,16 +6891,16 @@
         <f>IF($L153="","",M153-N153-O153-P153-Q153-R153-S153-T153)</f>
       </c>
       <c r="V153" s="3">
-        <f>IF($L153="","",(U153-X153)/K153*100)</f>
+        <f>IF($L153="","",(U153-AB153)/K153*100)</f>
       </c>
       <c r="W153" s="3">
         <f>IF($L153="","",N153-S153)</f>
       </c>
-      <c r="Y153" s="3">
-        <f>IF($L153="","",U153-X153)</f>
-      </c>
-    </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC153" s="3">
+        <f>IF($L153="","",U153-AB153)</f>
+      </c>
+    </row>
+    <row r="154" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="D154" s="2"/>
       <c r="K154" s="3"/>
@@ -6907,16 +6931,16 @@
         <f>IF($L154="","",M154-N154-O154-P154-Q154-R154-S154-T154)</f>
       </c>
       <c r="V154" s="3">
-        <f>IF($L154="","",(U154-X154)/K154*100)</f>
+        <f>IF($L154="","",(U154-AB154)/K154*100)</f>
       </c>
       <c r="W154" s="3">
         <f>IF($L154="","",N154-S154)</f>
       </c>
-      <c r="Y154" s="3">
-        <f>IF($L154="","",U154-X154)</f>
-      </c>
-    </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC154" s="3">
+        <f>IF($L154="","",U154-AB154)</f>
+      </c>
+    </row>
+    <row r="155" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="D155" s="2"/>
       <c r="K155" s="3"/>
@@ -6947,16 +6971,16 @@
         <f>IF($L155="","",M155-N155-O155-P155-Q155-R155-S155-T155)</f>
       </c>
       <c r="V155" s="3">
-        <f>IF($L155="","",(U155-X155)/K155*100)</f>
+        <f>IF($L155="","",(U155-AB155)/K155*100)</f>
       </c>
       <c r="W155" s="3">
         <f>IF($L155="","",N155-S155)</f>
       </c>
-      <c r="Y155" s="3">
-        <f>IF($L155="","",U155-X155)</f>
-      </c>
-    </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC155" s="3">
+        <f>IF($L155="","",U155-AB155)</f>
+      </c>
+    </row>
+    <row r="156" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="D156" s="2"/>
       <c r="K156" s="3"/>
@@ -6987,16 +7011,16 @@
         <f>IF($L156="","",M156-N156-O156-P156-Q156-R156-S156-T156)</f>
       </c>
       <c r="V156" s="3">
-        <f>IF($L156="","",(U156-X156)/K156*100)</f>
+        <f>IF($L156="","",(U156-AB156)/K156*100)</f>
       </c>
       <c r="W156" s="3">
         <f>IF($L156="","",N156-S156)</f>
       </c>
-      <c r="Y156" s="3">
-        <f>IF($L156="","",U156-X156)</f>
-      </c>
-    </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC156" s="3">
+        <f>IF($L156="","",U156-AB156)</f>
+      </c>
+    </row>
+    <row r="157" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="D157" s="2"/>
       <c r="K157" s="3"/>
@@ -7027,16 +7051,16 @@
         <f>IF($L157="","",M157-N157-O157-P157-Q157-R157-S157-T157)</f>
       </c>
       <c r="V157" s="3">
-        <f>IF($L157="","",(U157-X157)/K157*100)</f>
+        <f>IF($L157="","",(U157-AB157)/K157*100)</f>
       </c>
       <c r="W157" s="3">
         <f>IF($L157="","",N157-S157)</f>
       </c>
-      <c r="Y157" s="3">
-        <f>IF($L157="","",U157-X157)</f>
-      </c>
-    </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC157" s="3">
+        <f>IF($L157="","",U157-AB157)</f>
+      </c>
+    </row>
+    <row r="158" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="D158" s="2"/>
       <c r="K158" s="3"/>
@@ -7067,16 +7091,16 @@
         <f>IF($L158="","",M158-N158-O158-P158-Q158-R158-S158-T158)</f>
       </c>
       <c r="V158" s="3">
-        <f>IF($L158="","",(U158-X158)/K158*100)</f>
+        <f>IF($L158="","",(U158-AB158)/K158*100)</f>
       </c>
       <c r="W158" s="3">
         <f>IF($L158="","",N158-S158)</f>
       </c>
-      <c r="Y158" s="3">
-        <f>IF($L158="","",U158-X158)</f>
-      </c>
-    </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC158" s="3">
+        <f>IF($L158="","",U158-AB158)</f>
+      </c>
+    </row>
+    <row r="159" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="D159" s="2"/>
       <c r="K159" s="3"/>
@@ -7107,16 +7131,16 @@
         <f>IF($L159="","",M159-N159-O159-P159-Q159-R159-S159-T159)</f>
       </c>
       <c r="V159" s="3">
-        <f>IF($L159="","",(U159-X159)/K159*100)</f>
+        <f>IF($L159="","",(U159-AB159)/K159*100)</f>
       </c>
       <c r="W159" s="3">
         <f>IF($L159="","",N159-S159)</f>
       </c>
-      <c r="Y159" s="3">
-        <f>IF($L159="","",U159-X159)</f>
-      </c>
-    </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC159" s="3">
+        <f>IF($L159="","",U159-AB159)</f>
+      </c>
+    </row>
+    <row r="160" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="D160" s="2"/>
       <c r="K160" s="3"/>
@@ -7147,16 +7171,16 @@
         <f>IF($L160="","",M160-N160-O160-P160-Q160-R160-S160-T160)</f>
       </c>
       <c r="V160" s="3">
-        <f>IF($L160="","",(U160-X160)/K160*100)</f>
+        <f>IF($L160="","",(U160-AB160)/K160*100)</f>
       </c>
       <c r="W160" s="3">
         <f>IF($L160="","",N160-S160)</f>
       </c>
-      <c r="Y160" s="3">
-        <f>IF($L160="","",U160-X160)</f>
-      </c>
-    </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC160" s="3">
+        <f>IF($L160="","",U160-AB160)</f>
+      </c>
+    </row>
+    <row r="161" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="D161" s="2"/>
       <c r="K161" s="3"/>
@@ -7187,16 +7211,16 @@
         <f>IF($L161="","",M161-N161-O161-P161-Q161-R161-S161-T161)</f>
       </c>
       <c r="V161" s="3">
-        <f>IF($L161="","",(U161-X161)/K161*100)</f>
+        <f>IF($L161="","",(U161-AB161)/K161*100)</f>
       </c>
       <c r="W161" s="3">
         <f>IF($L161="","",N161-S161)</f>
       </c>
-      <c r="Y161" s="3">
-        <f>IF($L161="","",U161-X161)</f>
-      </c>
-    </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC161" s="3">
+        <f>IF($L161="","",U161-AB161)</f>
+      </c>
+    </row>
+    <row r="162" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="D162" s="2"/>
       <c r="K162" s="3"/>
@@ -7227,16 +7251,16 @@
         <f>IF($L162="","",M162-N162-O162-P162-Q162-R162-S162-T162)</f>
       </c>
       <c r="V162" s="3">
-        <f>IF($L162="","",(U162-X162)/K162*100)</f>
+        <f>IF($L162="","",(U162-AB162)/K162*100)</f>
       </c>
       <c r="W162" s="3">
         <f>IF($L162="","",N162-S162)</f>
       </c>
-      <c r="Y162" s="3">
-        <f>IF($L162="","",U162-X162)</f>
-      </c>
-    </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC162" s="3">
+        <f>IF($L162="","",U162-AB162)</f>
+      </c>
+    </row>
+    <row r="163" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="D163" s="2"/>
       <c r="K163" s="3"/>
@@ -7267,16 +7291,16 @@
         <f>IF($L163="","",M163-N163-O163-P163-Q163-R163-S163-T163)</f>
       </c>
       <c r="V163" s="3">
-        <f>IF($L163="","",(U163-X163)/K163*100)</f>
+        <f>IF($L163="","",(U163-AB163)/K163*100)</f>
       </c>
       <c r="W163" s="3">
         <f>IF($L163="","",N163-S163)</f>
       </c>
-      <c r="Y163" s="3">
-        <f>IF($L163="","",U163-X163)</f>
-      </c>
-    </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC163" s="3">
+        <f>IF($L163="","",U163-AB163)</f>
+      </c>
+    </row>
+    <row r="164" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="D164" s="2"/>
       <c r="K164" s="3"/>
@@ -7307,16 +7331,16 @@
         <f>IF($L164="","",M164-N164-O164-P164-Q164-R164-S164-T164)</f>
       </c>
       <c r="V164" s="3">
-        <f>IF($L164="","",(U164-X164)/K164*100)</f>
+        <f>IF($L164="","",(U164-AB164)/K164*100)</f>
       </c>
       <c r="W164" s="3">
         <f>IF($L164="","",N164-S164)</f>
       </c>
-      <c r="Y164" s="3">
-        <f>IF($L164="","",U164-X164)</f>
-      </c>
-    </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC164" s="3">
+        <f>IF($L164="","",U164-AB164)</f>
+      </c>
+    </row>
+    <row r="165" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="D165" s="2"/>
       <c r="K165" s="3"/>
@@ -7347,16 +7371,16 @@
         <f>IF($L165="","",M165-N165-O165-P165-Q165-R165-S165-T165)</f>
       </c>
       <c r="V165" s="3">
-        <f>IF($L165="","",(U165-X165)/K165*100)</f>
+        <f>IF($L165="","",(U165-AB165)/K165*100)</f>
       </c>
       <c r="W165" s="3">
         <f>IF($L165="","",N165-S165)</f>
       </c>
-      <c r="Y165" s="3">
-        <f>IF($L165="","",U165-X165)</f>
-      </c>
-    </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC165" s="3">
+        <f>IF($L165="","",U165-AB165)</f>
+      </c>
+    </row>
+    <row r="166" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="D166" s="2"/>
       <c r="K166" s="3"/>
@@ -7387,16 +7411,16 @@
         <f>IF($L166="","",M166-N166-O166-P166-Q166-R166-S166-T166)</f>
       </c>
       <c r="V166" s="3">
-        <f>IF($L166="","",(U166-X166)/K166*100)</f>
+        <f>IF($L166="","",(U166-AB166)/K166*100)</f>
       </c>
       <c r="W166" s="3">
         <f>IF($L166="","",N166-S166)</f>
       </c>
-      <c r="Y166" s="3">
-        <f>IF($L166="","",U166-X166)</f>
-      </c>
-    </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC166" s="3">
+        <f>IF($L166="","",U166-AB166)</f>
+      </c>
+    </row>
+    <row r="167" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="D167" s="2"/>
       <c r="K167" s="3"/>
@@ -7427,16 +7451,16 @@
         <f>IF($L167="","",M167-N167-O167-P167-Q167-R167-S167-T167)</f>
       </c>
       <c r="V167" s="3">
-        <f>IF($L167="","",(U167-X167)/K167*100)</f>
+        <f>IF($L167="","",(U167-AB167)/K167*100)</f>
       </c>
       <c r="W167" s="3">
         <f>IF($L167="","",N167-S167)</f>
       </c>
-      <c r="Y167" s="3">
-        <f>IF($L167="","",U167-X167)</f>
-      </c>
-    </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC167" s="3">
+        <f>IF($L167="","",U167-AB167)</f>
+      </c>
+    </row>
+    <row r="168" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="D168" s="2"/>
       <c r="K168" s="3"/>
@@ -7467,16 +7491,16 @@
         <f>IF($L168="","",M168-N168-O168-P168-Q168-R168-S168-T168)</f>
       </c>
       <c r="V168" s="3">
-        <f>IF($L168="","",(U168-X168)/K168*100)</f>
+        <f>IF($L168="","",(U168-AB168)/K168*100)</f>
       </c>
       <c r="W168" s="3">
         <f>IF($L168="","",N168-S168)</f>
       </c>
-      <c r="Y168" s="3">
-        <f>IF($L168="","",U168-X168)</f>
-      </c>
-    </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC168" s="3">
+        <f>IF($L168="","",U168-AB168)</f>
+      </c>
+    </row>
+    <row r="169" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="D169" s="2"/>
       <c r="K169" s="3"/>
@@ -7507,16 +7531,16 @@
         <f>IF($L169="","",M169-N169-O169-P169-Q169-R169-S169-T169)</f>
       </c>
       <c r="V169" s="3">
-        <f>IF($L169="","",(U169-X169)/K169*100)</f>
+        <f>IF($L169="","",(U169-AB169)/K169*100)</f>
       </c>
       <c r="W169" s="3">
         <f>IF($L169="","",N169-S169)</f>
       </c>
-      <c r="Y169" s="3">
-        <f>IF($L169="","",U169-X169)</f>
-      </c>
-    </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC169" s="3">
+        <f>IF($L169="","",U169-AB169)</f>
+      </c>
+    </row>
+    <row r="170" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="D170" s="2"/>
       <c r="K170" s="3"/>
@@ -7547,16 +7571,16 @@
         <f>IF($L170="","",M170-N170-O170-P170-Q170-R170-S170-T170)</f>
       </c>
       <c r="V170" s="3">
-        <f>IF($L170="","",(U170-X170)/K170*100)</f>
+        <f>IF($L170="","",(U170-AB170)/K170*100)</f>
       </c>
       <c r="W170" s="3">
         <f>IF($L170="","",N170-S170)</f>
       </c>
-      <c r="Y170" s="3">
-        <f>IF($L170="","",U170-X170)</f>
-      </c>
-    </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC170" s="3">
+        <f>IF($L170="","",U170-AB170)</f>
+      </c>
+    </row>
+    <row r="171" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="D171" s="2"/>
       <c r="K171" s="3"/>
@@ -7587,16 +7611,16 @@
         <f>IF($L171="","",M171-N171-O171-P171-Q171-R171-S171-T171)</f>
       </c>
       <c r="V171" s="3">
-        <f>IF($L171="","",(U171-X171)/K171*100)</f>
+        <f>IF($L171="","",(U171-AB171)/K171*100)</f>
       </c>
       <c r="W171" s="3">
         <f>IF($L171="","",N171-S171)</f>
       </c>
-      <c r="Y171" s="3">
-        <f>IF($L171="","",U171-X171)</f>
-      </c>
-    </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC171" s="3">
+        <f>IF($L171="","",U171-AB171)</f>
+      </c>
+    </row>
+    <row r="172" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="D172" s="2"/>
       <c r="K172" s="3"/>
@@ -7627,16 +7651,16 @@
         <f>IF($L172="","",M172-N172-O172-P172-Q172-R172-S172-T172)</f>
       </c>
       <c r="V172" s="3">
-        <f>IF($L172="","",(U172-X172)/K172*100)</f>
+        <f>IF($L172="","",(U172-AB172)/K172*100)</f>
       </c>
       <c r="W172" s="3">
         <f>IF($L172="","",N172-S172)</f>
       </c>
-      <c r="Y172" s="3">
-        <f>IF($L172="","",U172-X172)</f>
-      </c>
-    </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC172" s="3">
+        <f>IF($L172="","",U172-AB172)</f>
+      </c>
+    </row>
+    <row r="173" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="D173" s="2"/>
       <c r="K173" s="3"/>
@@ -7667,16 +7691,16 @@
         <f>IF($L173="","",M173-N173-O173-P173-Q173-R173-S173-T173)</f>
       </c>
       <c r="V173" s="3">
-        <f>IF($L173="","",(U173-X173)/K173*100)</f>
+        <f>IF($L173="","",(U173-AB173)/K173*100)</f>
       </c>
       <c r="W173" s="3">
         <f>IF($L173="","",N173-S173)</f>
       </c>
-      <c r="Y173" s="3">
-        <f>IF($L173="","",U173-X173)</f>
-      </c>
-    </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC173" s="3">
+        <f>IF($L173="","",U173-AB173)</f>
+      </c>
+    </row>
+    <row r="174" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="D174" s="2"/>
       <c r="K174" s="3"/>
@@ -7707,16 +7731,16 @@
         <f>IF($L174="","",M174-N174-O174-P174-Q174-R174-S174-T174)</f>
       </c>
       <c r="V174" s="3">
-        <f>IF($L174="","",(U174-X174)/K174*100)</f>
+        <f>IF($L174="","",(U174-AB174)/K174*100)</f>
       </c>
       <c r="W174" s="3">
         <f>IF($L174="","",N174-S174)</f>
       </c>
-      <c r="Y174" s="3">
-        <f>IF($L174="","",U174-X174)</f>
-      </c>
-    </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC174" s="3">
+        <f>IF($L174="","",U174-AB174)</f>
+      </c>
+    </row>
+    <row r="175" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="D175" s="2"/>
       <c r="K175" s="3"/>
@@ -7747,16 +7771,16 @@
         <f>IF($L175="","",M175-N175-O175-P175-Q175-R175-S175-T175)</f>
       </c>
       <c r="V175" s="3">
-        <f>IF($L175="","",(U175-X175)/K175*100)</f>
+        <f>IF($L175="","",(U175-AB175)/K175*100)</f>
       </c>
       <c r="W175" s="3">
         <f>IF($L175="","",N175-S175)</f>
       </c>
-      <c r="Y175" s="3">
-        <f>IF($L175="","",U175-X175)</f>
-      </c>
-    </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC175" s="3">
+        <f>IF($L175="","",U175-AB175)</f>
+      </c>
+    </row>
+    <row r="176" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="D176" s="2"/>
       <c r="K176" s="3"/>
@@ -7787,16 +7811,16 @@
         <f>IF($L176="","",M176-N176-O176-P176-Q176-R176-S176-T176)</f>
       </c>
       <c r="V176" s="3">
-        <f>IF($L176="","",(U176-X176)/K176*100)</f>
+        <f>IF($L176="","",(U176-AB176)/K176*100)</f>
       </c>
       <c r="W176" s="3">
         <f>IF($L176="","",N176-S176)</f>
       </c>
-      <c r="Y176" s="3">
-        <f>IF($L176="","",U176-X176)</f>
-      </c>
-    </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC176" s="3">
+        <f>IF($L176="","",U176-AB176)</f>
+      </c>
+    </row>
+    <row r="177" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="D177" s="2"/>
       <c r="K177" s="3"/>
@@ -7827,16 +7851,16 @@
         <f>IF($L177="","",M177-N177-O177-P177-Q177-R177-S177-T177)</f>
       </c>
       <c r="V177" s="3">
-        <f>IF($L177="","",(U177-X177)/K177*100)</f>
+        <f>IF($L177="","",(U177-AB177)/K177*100)</f>
       </c>
       <c r="W177" s="3">
         <f>IF($L177="","",N177-S177)</f>
       </c>
-      <c r="Y177" s="3">
-        <f>IF($L177="","",U177-X177)</f>
-      </c>
-    </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC177" s="3">
+        <f>IF($L177="","",U177-AB177)</f>
+      </c>
+    </row>
+    <row r="178" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="D178" s="2"/>
       <c r="K178" s="3"/>
@@ -7867,16 +7891,16 @@
         <f>IF($L178="","",M178-N178-O178-P178-Q178-R178-S178-T178)</f>
       </c>
       <c r="V178" s="3">
-        <f>IF($L178="","",(U178-X178)/K178*100)</f>
+        <f>IF($L178="","",(U178-AB178)/K178*100)</f>
       </c>
       <c r="W178" s="3">
         <f>IF($L178="","",N178-S178)</f>
       </c>
-      <c r="Y178" s="3">
-        <f>IF($L178="","",U178-X178)</f>
-      </c>
-    </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC178" s="3">
+        <f>IF($L178="","",U178-AB178)</f>
+      </c>
+    </row>
+    <row r="179" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="D179" s="2"/>
       <c r="K179" s="3"/>
@@ -7907,16 +7931,16 @@
         <f>IF($L179="","",M179-N179-O179-P179-Q179-R179-S179-T179)</f>
       </c>
       <c r="V179" s="3">
-        <f>IF($L179="","",(U179-X179)/K179*100)</f>
+        <f>IF($L179="","",(U179-AB179)/K179*100)</f>
       </c>
       <c r="W179" s="3">
         <f>IF($L179="","",N179-S179)</f>
       </c>
-      <c r="Y179" s="3">
-        <f>IF($L179="","",U179-X179)</f>
-      </c>
-    </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC179" s="3">
+        <f>IF($L179="","",U179-AB179)</f>
+      </c>
+    </row>
+    <row r="180" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="D180" s="2"/>
       <c r="K180" s="3"/>
@@ -7947,16 +7971,16 @@
         <f>IF($L180="","",M180-N180-O180-P180-Q180-R180-S180-T180)</f>
       </c>
       <c r="V180" s="3">
-        <f>IF($L180="","",(U180-X180)/K180*100)</f>
+        <f>IF($L180="","",(U180-AB180)/K180*100)</f>
       </c>
       <c r="W180" s="3">
         <f>IF($L180="","",N180-S180)</f>
       </c>
-      <c r="Y180" s="3">
-        <f>IF($L180="","",U180-X180)</f>
-      </c>
-    </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC180" s="3">
+        <f>IF($L180="","",U180-AB180)</f>
+      </c>
+    </row>
+    <row r="181" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="D181" s="2"/>
       <c r="K181" s="3"/>
@@ -7987,16 +8011,16 @@
         <f>IF($L181="","",M181-N181-O181-P181-Q181-R181-S181-T181)</f>
       </c>
       <c r="V181" s="3">
-        <f>IF($L181="","",(U181-X181)/K181*100)</f>
+        <f>IF($L181="","",(U181-AB181)/K181*100)</f>
       </c>
       <c r="W181" s="3">
         <f>IF($L181="","",N181-S181)</f>
       </c>
-      <c r="Y181" s="3">
-        <f>IF($L181="","",U181-X181)</f>
-      </c>
-    </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC181" s="3">
+        <f>IF($L181="","",U181-AB181)</f>
+      </c>
+    </row>
+    <row r="182" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="D182" s="2"/>
       <c r="K182" s="3"/>
@@ -8027,16 +8051,16 @@
         <f>IF($L182="","",M182-N182-O182-P182-Q182-R182-S182-T182)</f>
       </c>
       <c r="V182" s="3">
-        <f>IF($L182="","",(U182-X182)/K182*100)</f>
+        <f>IF($L182="","",(U182-AB182)/K182*100)</f>
       </c>
       <c r="W182" s="3">
         <f>IF($L182="","",N182-S182)</f>
       </c>
-      <c r="Y182" s="3">
-        <f>IF($L182="","",U182-X182)</f>
-      </c>
-    </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC182" s="3">
+        <f>IF($L182="","",U182-AB182)</f>
+      </c>
+    </row>
+    <row r="183" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="D183" s="2"/>
       <c r="K183" s="3"/>
@@ -8067,16 +8091,16 @@
         <f>IF($L183="","",M183-N183-O183-P183-Q183-R183-S183-T183)</f>
       </c>
       <c r="V183" s="3">
-        <f>IF($L183="","",(U183-X183)/K183*100)</f>
+        <f>IF($L183="","",(U183-AB183)/K183*100)</f>
       </c>
       <c r="W183" s="3">
         <f>IF($L183="","",N183-S183)</f>
       </c>
-      <c r="Y183" s="3">
-        <f>IF($L183="","",U183-X183)</f>
-      </c>
-    </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC183" s="3">
+        <f>IF($L183="","",U183-AB183)</f>
+      </c>
+    </row>
+    <row r="184" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="D184" s="2"/>
       <c r="K184" s="3"/>
@@ -8107,16 +8131,16 @@
         <f>IF($L184="","",M184-N184-O184-P184-Q184-R184-S184-T184)</f>
       </c>
       <c r="V184" s="3">
-        <f>IF($L184="","",(U184-X184)/K184*100)</f>
+        <f>IF($L184="","",(U184-AB184)/K184*100)</f>
       </c>
       <c r="W184" s="3">
         <f>IF($L184="","",N184-S184)</f>
       </c>
-      <c r="Y184" s="3">
-        <f>IF($L184="","",U184-X184)</f>
-      </c>
-    </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC184" s="3">
+        <f>IF($L184="","",U184-AB184)</f>
+      </c>
+    </row>
+    <row r="185" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="D185" s="2"/>
       <c r="K185" s="3"/>
@@ -8147,16 +8171,16 @@
         <f>IF($L185="","",M185-N185-O185-P185-Q185-R185-S185-T185)</f>
       </c>
       <c r="V185" s="3">
-        <f>IF($L185="","",(U185-X185)/K185*100)</f>
+        <f>IF($L185="","",(U185-AB185)/K185*100)</f>
       </c>
       <c r="W185" s="3">
         <f>IF($L185="","",N185-S185)</f>
       </c>
-      <c r="Y185" s="3">
-        <f>IF($L185="","",U185-X185)</f>
-      </c>
-    </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC185" s="3">
+        <f>IF($L185="","",U185-AB185)</f>
+      </c>
+    </row>
+    <row r="186" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="D186" s="2"/>
       <c r="K186" s="3"/>
@@ -8187,16 +8211,16 @@
         <f>IF($L186="","",M186-N186-O186-P186-Q186-R186-S186-T186)</f>
       </c>
       <c r="V186" s="3">
-        <f>IF($L186="","",(U186-X186)/K186*100)</f>
+        <f>IF($L186="","",(U186-AB186)/K186*100)</f>
       </c>
       <c r="W186" s="3">
         <f>IF($L186="","",N186-S186)</f>
       </c>
-      <c r="Y186" s="3">
-        <f>IF($L186="","",U186-X186)</f>
-      </c>
-    </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC186" s="3">
+        <f>IF($L186="","",U186-AB186)</f>
+      </c>
+    </row>
+    <row r="187" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="D187" s="2"/>
       <c r="K187" s="3"/>
@@ -8227,16 +8251,16 @@
         <f>IF($L187="","",M187-N187-O187-P187-Q187-R187-S187-T187)</f>
       </c>
       <c r="V187" s="3">
-        <f>IF($L187="","",(U187-X187)/K187*100)</f>
+        <f>IF($L187="","",(U187-AB187)/K187*100)</f>
       </c>
       <c r="W187" s="3">
         <f>IF($L187="","",N187-S187)</f>
       </c>
-      <c r="Y187" s="3">
-        <f>IF($L187="","",U187-X187)</f>
-      </c>
-    </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC187" s="3">
+        <f>IF($L187="","",U187-AB187)</f>
+      </c>
+    </row>
+    <row r="188" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="D188" s="2"/>
       <c r="K188" s="3"/>
@@ -8267,16 +8291,16 @@
         <f>IF($L188="","",M188-N188-O188-P188-Q188-R188-S188-T188)</f>
       </c>
       <c r="V188" s="3">
-        <f>IF($L188="","",(U188-X188)/K188*100)</f>
+        <f>IF($L188="","",(U188-AB188)/K188*100)</f>
       </c>
       <c r="W188" s="3">
         <f>IF($L188="","",N188-S188)</f>
       </c>
-      <c r="Y188" s="3">
-        <f>IF($L188="","",U188-X188)</f>
-      </c>
-    </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC188" s="3">
+        <f>IF($L188="","",U188-AB188)</f>
+      </c>
+    </row>
+    <row r="189" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="D189" s="2"/>
       <c r="K189" s="3"/>
@@ -8307,16 +8331,16 @@
         <f>IF($L189="","",M189-N189-O189-P189-Q189-R189-S189-T189)</f>
       </c>
       <c r="V189" s="3">
-        <f>IF($L189="","",(U189-X189)/K189*100)</f>
+        <f>IF($L189="","",(U189-AB189)/K189*100)</f>
       </c>
       <c r="W189" s="3">
         <f>IF($L189="","",N189-S189)</f>
       </c>
-      <c r="Y189" s="3">
-        <f>IF($L189="","",U189-X189)</f>
-      </c>
-    </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC189" s="3">
+        <f>IF($L189="","",U189-AB189)</f>
+      </c>
+    </row>
+    <row r="190" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="D190" s="2"/>
       <c r="K190" s="3"/>
@@ -8347,16 +8371,16 @@
         <f>IF($L190="","",M190-N190-O190-P190-Q190-R190-S190-T190)</f>
       </c>
       <c r="V190" s="3">
-        <f>IF($L190="","",(U190-X190)/K190*100)</f>
+        <f>IF($L190="","",(U190-AB190)/K190*100)</f>
       </c>
       <c r="W190" s="3">
         <f>IF($L190="","",N190-S190)</f>
       </c>
-      <c r="Y190" s="3">
-        <f>IF($L190="","",U190-X190)</f>
-      </c>
-    </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC190" s="3">
+        <f>IF($L190="","",U190-AB190)</f>
+      </c>
+    </row>
+    <row r="191" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="D191" s="2"/>
       <c r="K191" s="3"/>
@@ -8387,16 +8411,16 @@
         <f>IF($L191="","",M191-N191-O191-P191-Q191-R191-S191-T191)</f>
       </c>
       <c r="V191" s="3">
-        <f>IF($L191="","",(U191-X191)/K191*100)</f>
+        <f>IF($L191="","",(U191-AB191)/K191*100)</f>
       </c>
       <c r="W191" s="3">
         <f>IF($L191="","",N191-S191)</f>
       </c>
-      <c r="Y191" s="3">
-        <f>IF($L191="","",U191-X191)</f>
-      </c>
-    </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC191" s="3">
+        <f>IF($L191="","",U191-AB191)</f>
+      </c>
+    </row>
+    <row r="192" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="D192" s="2"/>
       <c r="K192" s="3"/>
@@ -8427,16 +8451,16 @@
         <f>IF($L192="","",M192-N192-O192-P192-Q192-R192-S192-T192)</f>
       </c>
       <c r="V192" s="3">
-        <f>IF($L192="","",(U192-X192)/K192*100)</f>
+        <f>IF($L192="","",(U192-AB192)/K192*100)</f>
       </c>
       <c r="W192" s="3">
         <f>IF($L192="","",N192-S192)</f>
       </c>
-      <c r="Y192" s="3">
-        <f>IF($L192="","",U192-X192)</f>
-      </c>
-    </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC192" s="3">
+        <f>IF($L192="","",U192-AB192)</f>
+      </c>
+    </row>
+    <row r="193" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="D193" s="2"/>
       <c r="K193" s="3"/>
@@ -8467,16 +8491,16 @@
         <f>IF($L193="","",M193-N193-O193-P193-Q193-R193-S193-T193)</f>
       </c>
       <c r="V193" s="3">
-        <f>IF($L193="","",(U193-X193)/K193*100)</f>
+        <f>IF($L193="","",(U193-AB193)/K193*100)</f>
       </c>
       <c r="W193" s="3">
         <f>IF($L193="","",N193-S193)</f>
       </c>
-      <c r="Y193" s="3">
-        <f>IF($L193="","",U193-X193)</f>
-      </c>
-    </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC193" s="3">
+        <f>IF($L193="","",U193-AB193)</f>
+      </c>
+    </row>
+    <row r="194" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="D194" s="2"/>
       <c r="K194" s="3"/>
@@ -8507,16 +8531,16 @@
         <f>IF($L194="","",M194-N194-O194-P194-Q194-R194-S194-T194)</f>
       </c>
       <c r="V194" s="3">
-        <f>IF($L194="","",(U194-X194)/K194*100)</f>
+        <f>IF($L194="","",(U194-AB194)/K194*100)</f>
       </c>
       <c r="W194" s="3">
         <f>IF($L194="","",N194-S194)</f>
       </c>
-      <c r="Y194" s="3">
-        <f>IF($L194="","",U194-X194)</f>
-      </c>
-    </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC194" s="3">
+        <f>IF($L194="","",U194-AB194)</f>
+      </c>
+    </row>
+    <row r="195" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="D195" s="2"/>
       <c r="K195" s="3"/>
@@ -8547,16 +8571,16 @@
         <f>IF($L195="","",M195-N195-O195-P195-Q195-R195-S195-T195)</f>
       </c>
       <c r="V195" s="3">
-        <f>IF($L195="","",(U195-X195)/K195*100)</f>
+        <f>IF($L195="","",(U195-AB195)/K195*100)</f>
       </c>
       <c r="W195" s="3">
         <f>IF($L195="","",N195-S195)</f>
       </c>
-      <c r="Y195" s="3">
-        <f>IF($L195="","",U195-X195)</f>
-      </c>
-    </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC195" s="3">
+        <f>IF($L195="","",U195-AB195)</f>
+      </c>
+    </row>
+    <row r="196" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="D196" s="2"/>
       <c r="K196" s="3"/>
@@ -8587,16 +8611,16 @@
         <f>IF($L196="","",M196-N196-O196-P196-Q196-R196-S196-T196)</f>
       </c>
       <c r="V196" s="3">
-        <f>IF($L196="","",(U196-X196)/K196*100)</f>
+        <f>IF($L196="","",(U196-AB196)/K196*100)</f>
       </c>
       <c r="W196" s="3">
         <f>IF($L196="","",N196-S196)</f>
       </c>
-      <c r="Y196" s="3">
-        <f>IF($L196="","",U196-X196)</f>
-      </c>
-    </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC196" s="3">
+        <f>IF($L196="","",U196-AB196)</f>
+      </c>
+    </row>
+    <row r="197" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="D197" s="2"/>
       <c r="K197" s="3"/>
@@ -8627,16 +8651,16 @@
         <f>IF($L197="","",M197-N197-O197-P197-Q197-R197-S197-T197)</f>
       </c>
       <c r="V197" s="3">
-        <f>IF($L197="","",(U197-X197)/K197*100)</f>
+        <f>IF($L197="","",(U197-AB197)/K197*100)</f>
       </c>
       <c r="W197" s="3">
         <f>IF($L197="","",N197-S197)</f>
       </c>
-      <c r="Y197" s="3">
-        <f>IF($L197="","",U197-X197)</f>
-      </c>
-    </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC197" s="3">
+        <f>IF($L197="","",U197-AB197)</f>
+      </c>
+    </row>
+    <row r="198" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="D198" s="2"/>
       <c r="K198" s="3"/>
@@ -8667,16 +8691,16 @@
         <f>IF($L198="","",M198-N198-O198-P198-Q198-R198-S198-T198)</f>
       </c>
       <c r="V198" s="3">
-        <f>IF($L198="","",(U198-X198)/K198*100)</f>
+        <f>IF($L198="","",(U198-AB198)/K198*100)</f>
       </c>
       <c r="W198" s="3">
         <f>IF($L198="","",N198-S198)</f>
       </c>
-      <c r="Y198" s="3">
-        <f>IF($L198="","",U198-X198)</f>
-      </c>
-    </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC198" s="3">
+        <f>IF($L198="","",U198-AB198)</f>
+      </c>
+    </row>
+    <row r="199" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="D199" s="2"/>
       <c r="K199" s="3"/>
@@ -8707,16 +8731,16 @@
         <f>IF($L199="","",M199-N199-O199-P199-Q199-R199-S199-T199)</f>
       </c>
       <c r="V199" s="3">
-        <f>IF($L199="","",(U199-X199)/K199*100)</f>
+        <f>IF($L199="","",(U199-AB199)/K199*100)</f>
       </c>
       <c r="W199" s="3">
         <f>IF($L199="","",N199-S199)</f>
       </c>
-      <c r="Y199" s="3">
-        <f>IF($L199="","",U199-X199)</f>
-      </c>
-    </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC199" s="3">
+        <f>IF($L199="","",U199-AB199)</f>
+      </c>
+    </row>
+    <row r="200" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="D200" s="2"/>
       <c r="K200" s="3"/>
@@ -8747,16 +8771,16 @@
         <f>IF($L200="","",M200-N200-O200-P200-Q200-R200-S200-T200)</f>
       </c>
       <c r="V200" s="3">
-        <f>IF($L200="","",(U200-X200)/K200*100)</f>
+        <f>IF($L200="","",(U200-AB200)/K200*100)</f>
       </c>
       <c r="W200" s="3">
         <f>IF($L200="","",N200-S200)</f>
       </c>
-      <c r="Y200" s="3">
-        <f>IF($L200="","",U200-X200)</f>
-      </c>
-    </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC200" s="3">
+        <f>IF($L200="","",U200-AB200)</f>
+      </c>
+    </row>
+    <row r="201" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="D201" s="2"/>
       <c r="K201" s="3"/>
@@ -8787,16 +8811,16 @@
         <f>IF($L201="","",M201-N201-O201-P201-Q201-R201-S201-T201)</f>
       </c>
       <c r="V201" s="3">
-        <f>IF($L201="","",(U201-X201)/K201*100)</f>
+        <f>IF($L201="","",(U201-AB201)/K201*100)</f>
       </c>
       <c r="W201" s="3">
         <f>IF($L201="","",N201-S201)</f>
       </c>
-      <c r="Y201" s="3">
-        <f>IF($L201="","",U201-X201)</f>
-      </c>
-    </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="AC201" s="3">
+        <f>IF($L201="","",U201-AB201)</f>
+      </c>
+    </row>
+    <row r="202" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="D202" s="2"/>
       <c r="K202" s="3"/>
@@ -8827,18 +8851,18 @@
         <f>IF($L202="","",M202-N202-O202-P202-Q202-R202-S202-T202)</f>
       </c>
       <c r="V202" s="3">
-        <f>IF($L202="","",(U202-X202)/K202*100)</f>
+        <f>IF($L202="","",(U202-AB202)/K202*100)</f>
       </c>
       <c r="W202" s="3">
         <f>IF($L202="","",N202-S202)</f>
       </c>
-      <c r="Y202" s="3">
-        <f>IF($L202="","",U202-X202)</f>
-      </c>
-    </row>
-    <row r="203" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC202" s="3">
+        <f>IF($L202="","",U202-AB202)</f>
+      </c>
+    </row>
+    <row r="203" spans="1:34" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -8885,7 +8909,7 @@
         <f>SUM(U2:U202)</f>
       </c>
       <c r="V203" s="6">
-        <f>IFERROR((U203-X203)/K203*100,0)</f>
+        <f>IFERROR((U203-AB203)/K203*100,0)</f>
       </c>
       <c r="W203" s="6">
         <f>SUM(W2:W202)</f>
@@ -8896,11 +8920,23 @@
       <c r="Y203" s="6">
         <f>SUM(Y2:Y202)</f>
       </c>
-      <c r="Z203" s="4"/>
-      <c r="AA203" s="4"/>
-      <c r="AB203" s="4"/>
-      <c r="AC203" s="4"/>
+      <c r="Z203" s="6">
+        <f>SUM(Z2:Z202)</f>
+      </c>
+      <c r="AA203" s="6">
+        <f>SUM(AA2:AA202)</f>
+      </c>
+      <c r="AB203" s="6">
+        <f>SUM(AB2:AB202)</f>
+      </c>
+      <c r="AC203" s="6">
+        <f>SUM(AC2:AC202)</f>
+      </c>
       <c r="AD203" s="4"/>
+      <c r="AE203" s="4"/>
+      <c r="AF203" s="4"/>
+      <c r="AG203" s="4"/>
+      <c r="AH203" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
